--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__CARROUSEL TJ.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__CARROUSEL TJ.xlsx
@@ -1249,12 +1249,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>288411</t>
+          <t>267507</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>85909</t>
+          <t>65011</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1264,17 +1264,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>GAEL</t>
+          <t>YAZMIN</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>GUEVARA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1284,10 +1284,14 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6647417483</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>6647978403</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>C FCO I MADERO 6852-B</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1295,56 +1299,64 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>02-07-2004</t>
+          <t>05-07-1998</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>cacha1663@gmail.com</t>
+          <t>YAZMINLOPEZGUEVARA1998@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>16-04-2025 14:18:05</t>
+          <t>26-11-2024 06:55:59</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12-02-2026 14:59:54</t>
+          <t>22-02-2026 12:28:31</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr"/>
+          <t>22-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>22-02-2026 12:25:50</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W7" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1352,7 +1364,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26110522295360003155</t>
+          <t>26140522563020001629</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1363,12 +1375,12 @@
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Viridiana Ramirez</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1380,12 +1392,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>329849</t>
+          <t>288411</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14903</t>
+          <t>85909</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1395,17 +1407,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>IRVING</t>
+          <t>GAEL</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SERRATO</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1415,14 +1427,10 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6642868147</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
+          <t>6647417483</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1430,17 +1438,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>24-12-1999</t>
+          <t>02-07-2004</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>IRVINGSERRATO@GMAIL.COM</t>
+          <t>cacha1663@gmail.com</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>22-12-2025 11:12:53</t>
+          <t>16-04-2025 14:18:05</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1450,12 +1458,12 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1465,29 +1473,21 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>17-02-2026 17:42:13</t>
+          <t>12-02-2026 14:59:54</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>17-02-2026 17:41:29</t>
-        </is>
-      </c>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26120522438440007288</t>
+          <t>26110522295360003155</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Juan Antonio  Beltran Sanchez</t>
+          <t>Viridiana Ramirez</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1523,12 +1523,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>267507</t>
+          <t>329849</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>65011</t>
+          <t>14903</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1538,17 +1538,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>YAZMIN</t>
+          <t>IRVING</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>GUEVARA</t>
+          <t>SERRATO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1558,12 +1558,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6647978403</t>
+          <t>6642868147</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>C FCO I MADERO 6852-B</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1573,22 +1573,22 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>05-07-1998</t>
+          <t>24-12-1999</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>YAZMINLOPEZGUEVARA1998@GMAIL.COM</t>
+          <t>IRVINGSERRATO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>26-11-2024 06:55:59</t>
+          <t>22-12-2025 11:12:53</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1598,27 +1598,27 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>22-02-2026 12:28:31</t>
+          <t>17-02-2026 17:42:13</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>22-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>22-02-2026 12:25:50</t>
+          <t>17-02-2026 17:41:29</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26140522563020001629</t>
+          <t>26120522438440007288</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1649,12 +1649,12 @@
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>Juan Antonio  Beltran Sanchez</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -2067,12 +2067,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>340762</t>
+          <t>182978</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>18580</t>
+          <t>80485</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2082,17 +2082,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HILDA</t>
+          <t>YADIRA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JANNET</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>ARCINIEGA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2102,67 +2102,63 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6642326055</t>
+          <t>6647017714</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>FLORIDO</t>
+          <t>EMPERADORES</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>16-04-1978</t>
+          <t>03-07-2006</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>HILDASILVA2716@GMAIL.COM</t>
+          <t>01209063@COBACHBC.EDU</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>03-02-2026 18:00:36</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-07-2023 14:59:17</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>03-02-2026 18:03:29</t>
+          <t>02-02-2026 12:32:41</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>03-02-2026 18:02:44</t>
+          <t>02-02-2026 12:32:16</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2172,7 +2168,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2182,19 +2178,19 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26110522051620002386</t>
+          <t>26110522009010002226</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Viridiana Ramirez</t>
+          <t>Arid Alexis Tolin Caldera</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2206,12 +2202,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>182978</t>
+          <t>259436</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>80485</t>
+          <t>56940</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2221,17 +2217,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>YADIRA</t>
+          <t xml:space="preserve">FRIDA SOFIA </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t xml:space="preserve">BETANCOURT </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ARCINIEGA</t>
+          <t>VILLA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2241,14 +2237,10 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6647017714</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>EMPERADORES</t>
-        </is>
-      </c>
+          <t>6648246360</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2256,60 +2248,56 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>03-07-2006</t>
+          <t>24-08-2009</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>01209063@COBACHBC.EDU</t>
+          <t>BETANCOURTFRIDA79@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>10-07-2023 14:59:17</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>28-09-2024 11:57:38</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>02-02-2026 12:32:41</t>
+          <t>24-02-2026 19:14:17</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>02-02-2026 12:32:16</t>
-        </is>
-      </c>
+          <t>24-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2317,19 +2305,19 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26110522009010002226</t>
+          <t>26110522633860003956</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Arid Alexis Tolin Caldera</t>
+          <t>Alan Rene Flores Wong</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2341,12 +2329,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>259436</t>
+          <t>340762</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>56940</t>
+          <t>18580</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2356,17 +2344,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRIDA SOFIA </t>
+          <t>HILDA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">BETANCOURT </t>
+          <t>JANNET</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>VILLA</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2376,67 +2364,79 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6648246360</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>6642326055</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>FLORIDO</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>24-08-2009</t>
+          <t>16-04-1978</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>BETANCOURTFRIDA79@GMAIL.COM</t>
+          <t>HILDASILVA2716@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>28-09-2024 11:57:38</t>
+          <t>03-02-2026 18:00:36</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>24-02-2026 19:14:17</t>
+          <t>03-02-2026 18:03:29</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr"/>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>03-02-2026 18:02:44</t>
+        </is>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2444,19 +2444,19 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26110522633860003956</t>
+          <t>26110522051620002386</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Alan Rene Flores Wong</t>
+          <t>Viridiana Ramirez</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2603,12 +2603,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>340526</t>
+          <t>285211</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>18344</t>
+          <t>82712</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2618,17 +2618,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">KIARA </t>
+          <t>JOSÉ ALBERTO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>PILO</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>IRAZOQUI</t>
+          <t>MANZO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2638,63 +2638,67 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6647461073</t>
+          <t>6631059616</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t xml:space="preserve">SANCHEZ </t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>21-11-2004</t>
+          <t>03-12-2006</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>21KIARARI@GMAIL.COM</t>
+          <t>PILOMANZO1244@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>03-02-2026 11:42:06</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>27-03-2025 12:53:54</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>03-02-2026 11:44:35</t>
+          <t>24-02-2026 19:25:06</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>24-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>03-02-2026 11:44:10</t>
+          <t>24-02-2026 19:24:30</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2714,19 +2718,23 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26110522037410002329</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr"/>
+          <t>26110522634410003958</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Marissa  Hernandez Galindo</t>
+          <t>Alan Rene Flores Wong</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2738,12 +2746,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>340692</t>
+          <t>340526</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>18510</t>
+          <t>18344</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2753,17 +2761,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FRANYA JOSELIN</t>
+          <t xml:space="preserve">KIARA </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ALCANTARA</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t>IRAZOQUI</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2773,10 +2781,14 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6646106426</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>6647461073</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2784,42 +2796,38 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>17-06-2008</t>
+          <t>21-11-2004</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>ALCANTARAVALENZUELAFRANYA@GMAIL.COM</t>
+          <t>21KIARARI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>03-02-2026 16:55:41</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>03-02-2026 11:42:06</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>03-02-2026 16:56:27</t>
+          <t>03-02-2026 11:44:35</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2827,13 +2835,21 @@
           <t>03-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>03-02-2026 11:44:10</t>
+        </is>
+      </c>
       <c r="U18" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2841,19 +2857,19 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26110522047320002374</t>
+          <t>26110522037410002329</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Yadira Polo</t>
+          <t>Marissa  Hernandez Galindo</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2865,12 +2881,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>285211</t>
+          <t>340692</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>82712</t>
+          <t>18510</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2880,17 +2896,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>JOSÉ ALBERTO</t>
+          <t>FRANYA JOSELIN</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PILO</t>
+          <t>ALCANTARA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MANZO</t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2900,32 +2916,28 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6631059616</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SANCHEZ </t>
-        </is>
-      </c>
+          <t>6646106426</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>03-12-2006</t>
+          <t>17-06-2008</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>PILOMANZO1244@GMAIL.COM</t>
+          <t>ALCANTARAVALENZUELAFRANYA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>27-03-2025 12:53:54</t>
+          <t>03-02-2026 16:55:41</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2935,44 +2947,36 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>24-02-2026 19:25:06</t>
+          <t>03-02-2026 16:56:27</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>24-02-2026 19:24:30</t>
-        </is>
-      </c>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2980,23 +2984,19 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26110522634410003958</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26110522047320002374</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Alan Rene Flores Wong</t>
+          <t>Yadira Polo</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -4751,12 +4751,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>342415</t>
+          <t>322907</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20233</t>
+          <t>19846</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4766,17 +4766,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NORMA</t>
+          <t>FIDEL</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ACOSTA</t>
+          <t>CARRANZA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4786,35 +4786,39 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6643629695</t>
+          <t>6634341922</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>SANCHEZ TABOADA</t>
+          <t>ZONA ESTE</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>12-03-1985</t>
+          <t>02-04-2011</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>MEACNO11@GMAIL.COM</t>
+          <t>FCARRAZAPARTIDA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>09-02-2026 18:59:19</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>10-11-2025 15:09:07</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O33" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -4822,7 +4826,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -4832,17 +4836,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>11-02-2026 19:08:28</t>
+          <t>24-02-2026 15:53:22</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>24-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>11-02-2026 19:07:54</t>
+          <t>24-02-2026 15:52:17</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4862,7 +4866,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26110522276090003099</t>
+          <t>26110522623110003914</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -4878,24 +4882,24 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Alan Rene Flores Wong</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>342417</t>
+          <t>342415</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20235</t>
+          <t>20233</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4905,19 +4909,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>JUANA</t>
+          <t>NORMA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t>ACOSTA</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t>MEDINA</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>SANTOYO</t>
-        </is>
-      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>52</t>
@@ -4925,7 +4929,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>7581070574</t>
+          <t>6643629695</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4940,17 +4944,17 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>09-05-1964</t>
+          <t>12-03-1985</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>JUANAMEDINASANTOYO@GMAIL.COM</t>
+          <t>MEACNO11@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>09-02-2026 18:59:33</t>
+          <t>09-02-2026 18:59:19</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4971,7 +4975,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>11-02-2026 19:05:05</t>
+          <t>11-02-2026 19:08:28</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4981,7 +4985,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>11-02-2026 19:03:53</t>
+          <t>11-02-2026 19:07:54</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -5001,7 +5005,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26110522275950003097</t>
+          <t>26110522276090003099</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -5017,7 +5021,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Viridiana Ramirez</t>
+          <t>Alan Rene Flores Wong</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5029,12 +5033,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>342535</t>
+          <t>342417</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20352</t>
+          <t>20235</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5044,17 +5048,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>TERESA</t>
+          <t>JUANA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AVENDAÑO</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>SANTOYO</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5064,12 +5068,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6636220816</t>
+          <t>7581070574</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>ARTICULO 2DO</t>
+          <t>SANCHEZ TABOADA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5079,17 +5083,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>01-08-1986</t>
+          <t>09-05-1964</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>AVENDANORODRIGUEZTERESA@GMAIL.COM</t>
+          <t>JUANAMEDINASANTOYO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>10-02-2026 07:38:55</t>
+          <t>09-02-2026 18:59:33</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -5100,7 +5104,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -5110,7 +5114,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>11-02-2026 10:43:14</t>
+          <t>11-02-2026 19:05:05</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -5120,7 +5124,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>11-02-2026 10:42:47</t>
+          <t>11-02-2026 19:03:53</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5140,19 +5144,15 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26110522261640003039</t>
+          <t>26110522275950003097</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>JAIME ARTURO TENA HUERTA</t>
-        </is>
-      </c>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
           <t>499</t>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Marissa  Hernandez Galindo</t>
+          <t>Viridiana Ramirez</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5172,12 +5172,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>322907</t>
+          <t>342535</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>19846</t>
+          <t>20352</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5187,17 +5187,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>FIDEL</t>
+          <t>TERESA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CARRANZA</t>
+          <t>AVENDAÑO</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PARTIDA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5207,39 +5207,35 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6634341922</t>
+          <t>6636220816</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>ZONA ESTE</t>
+          <t>ARTICULO 2DO</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>02-04-2011</t>
+          <t>01-08-1986</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>FCARRAZAPARTIDA@GMAIL.COM</t>
+          <t>AVENDANORODRIGUEZTERESA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>10-11-2025 15:09:07</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>10-02-2026 07:38:55</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5257,17 +5253,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>24-02-2026 15:53:22</t>
+          <t>11-02-2026 10:43:14</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>24-02-2026 15:52:17</t>
+          <t>11-02-2026 10:42:47</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -5287,15 +5283,19 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26110522623110003914</t>
+          <t>26110522261640003039</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>JAIME ARTURO TENA HUERTA</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>499</t>
@@ -5303,12 +5303,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Marissa  Hernandez Galindo</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -5585,12 +5585,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>340072</t>
+          <t>340496</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>17890</t>
+          <t>18314</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5600,17 +5600,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">MELINA </t>
+          <t>PEDRO ALFREDO</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCIO </t>
+          <t>MAZABA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNNADEZ </t>
+          <t>CAMPECHANO</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5620,32 +5620,32 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6642636703</t>
+          <t>6641241235</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMINO VERDE </t>
+          <t>22163</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>01-09-1980</t>
+          <t>23-11-1998</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>MARIAGUADALUPE010989@GMAIL.COM</t>
+          <t>ALFREDO.MAZABA@AICLOD.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>02-02-2026 11:52:41</t>
+          <t>03-02-2026 09:45:56</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -5666,17 +5666,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>02-02-2026 11:55:14</t>
+          <t>03-02-2026 09:48:03</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>02-02-2026 11:54:50</t>
+          <t>03-02-2026 09:46:54</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26110522007870002222</t>
+          <t>26110522035510002321</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
@@ -5708,7 +5708,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Marissa  Hernandez Galindo</t>
+          <t xml:space="preserve"> Daniel  Salinas</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5720,12 +5720,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>340577</t>
+          <t>340072</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>18395</t>
+          <t>17890</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5735,17 +5735,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ALLISON</t>
+          <t xml:space="preserve">MELINA </t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t xml:space="preserve">LUCIO </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>KING</t>
+          <t xml:space="preserve">HERNNADEZ </t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5755,10 +5755,14 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6646984562</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>6642636703</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CAMINO VERDE </t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5766,56 +5770,60 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>06-03-2011</t>
+          <t>01-09-1980</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>VALERIAKINGDIRECTIONER@GMAIL.COM</t>
+          <t>MARIAGUADALUPE010989@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>03-02-2026 13:43:25</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>02-02-2026 11:52:41</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>10-02-2026 14:33:25</t>
+          <t>02-02-2026 11:55:14</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>02-02-2026 11:54:50</t>
+        </is>
+      </c>
       <c r="U40" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5823,27 +5831,19 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26110522232700002956</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>JAIME ARTURO TENA HUERTA</t>
-        </is>
-      </c>
+          <t>26110522007870002222</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Viridiana Ramirez</t>
+          <t>Marissa  Hernandez Galindo</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -5855,12 +5855,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>340025</t>
+          <t>340577</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>17843</t>
+          <t>18395</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5870,17 +5870,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ARLET BELINDA</t>
+          <t>ALLISON</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>BAUTISTA</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>BAUTISTA</t>
+          <t>KING</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5890,14 +5890,10 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>9531690085</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CENTRO  </t>
-        </is>
-      </c>
+          <t>6646984562</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5905,60 +5901,56 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>30-11-2004</t>
+          <t>06-03-2011</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>BELIBAUTISTA23@GMAIL.COM</t>
+          <t>VALERIAKINGDIRECTIONER@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>02-02-2026 10:48:19</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+          <t>03-02-2026 13:43:25</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>07-02-2026 15:52:39</t>
+          <t>10-02-2026 14:33:25</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>07-02-2026 15:51:57</t>
-        </is>
-      </c>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5966,18 +5958,22 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26110522162260002762</t>
+          <t>26110522232700002956</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>JAIME ARTURO TENA HUERTA</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
@@ -5994,12 +5990,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>340496</t>
+          <t>340025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>18314</t>
+          <t>17843</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6009,17 +6005,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>PEDRO ALFREDO</t>
+          <t>ARLET BELINDA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>MAZABA</t>
+          <t>BAUTISTA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CAMPECHANO</t>
+          <t>BAUTISTA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6029,32 +6025,32 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6641241235</t>
+          <t>9531690085</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>22163</t>
+          <t xml:space="preserve">CENTRO  </t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>23-11-1998</t>
+          <t>30-11-2004</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>ALFREDO.MAZABA@AICLOD.COM</t>
+          <t>BELIBAUTISTA23@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>03-02-2026 09:45:56</t>
+          <t>02-02-2026 10:48:19</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -6075,17 +6071,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>03-02-2026 09:48:03</t>
+          <t>07-02-2026 15:52:39</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>07-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>03-02-2026 09:46:54</t>
+          <t>07-02-2026 15:51:57</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -6105,10 +6101,14 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26110522035510002321</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr"/>
+          <t>26110522162260002762</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Daniel  Salinas</t>
+          <t>Viridiana Ramirez</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6129,12 +6129,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>341849</t>
+          <t>343621</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>19667</t>
+          <t>21438</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6144,17 +6144,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>AYLIN</t>
+          <t>ARGENIS ADRIAN</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANCHEZ </t>
+          <t>DURAZO</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve"> RUIZ</t>
+          <t>VALENCIA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6164,32 +6164,32 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>8113900646</t>
+          <t>6644768904</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>AV. POPOCATÉPETL</t>
+          <t>MATAMOROS</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>24-02-2004</t>
+          <t>06-10-1996</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>AGSR2402@GMAIL.COM</t>
+          <t>ARGENISSA6@GMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>07-02-2026 19:37:45</t>
+          <t>13-02-2026 22:06:53</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -6210,22 +6210,22 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>07-02-2026 19:37:46</t>
+          <t>13-02-2026 22:09:38</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>07-02-2026 19:37:46</t>
+          <t>13-02-2026 22:09:06</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26110522162300002765</t>
+          <t>26110522332060003290</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Yadira Polo</t>
+          <t>Alan Rene Flores Wong</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -6264,12 +6264,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>343621</t>
+          <t>341849</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>21438</t>
+          <t>19667</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6279,17 +6279,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ARGENIS ADRIAN</t>
+          <t>AYLIN</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>DURAZO</t>
+          <t xml:space="preserve">SANCHEZ </t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t xml:space="preserve"> RUIZ</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6299,32 +6299,32 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6644768904</t>
+          <t>8113900646</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>MATAMOROS</t>
+          <t>AV. POPOCATÉPETL</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>06-10-1996</t>
+          <t>24-02-2004</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>ARGENISSA6@GMAIL.COM</t>
+          <t>AGSR2402@GMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>13-02-2026 22:06:53</t>
+          <t>07-02-2026 19:37:45</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -6345,29 +6345,29 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>13-02-2026 22:09:38</t>
+          <t>07-02-2026 19:37:46</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>07-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>13-02-2026 22:09:06</t>
+          <t>07-02-2026 19:37:46</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="W44" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26110522332060003290</t>
+          <t>26110522162300002765</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr"/>
@@ -6387,7 +6387,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>Alan Rene Flores Wong</t>
+          <t>Yadira Polo</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -6399,12 +6399,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>342215</t>
+          <t>341118</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20033</t>
+          <t>18936</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6414,17 +6414,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">AMERICA </t>
+          <t xml:space="preserve">DAVID </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERRERA </t>
+          <t xml:space="preserve">SOTELO </t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEZA </t>
+          <t xml:space="preserve">MEDINA </t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6434,32 +6434,32 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6631239192</t>
+          <t>6643656598</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALLE DE LAS PALMAS </t>
+          <t>LA MESA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>11-03-2006</t>
+          <t>18-12-1983</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>AMERICAHERRERAMEZA@GMAIL.COM</t>
+          <t>SEDIVIDIOLACENA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>09-02-2026 15:32:32</t>
+          <t>04-02-2026 17:45:14</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>09-02-2026 15:36:39</t>
+          <t>04-02-2026 17:47:07</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>09-02-2026 15:36:02</t>
+          <t>04-02-2026 17:46:36</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26110522195800002832</t>
+          <t>26110522083440002492</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr"/>
@@ -6522,7 +6522,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Daniel  Salinas</t>
+          <t>Alan Rene Flores Wong</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -6534,12 +6534,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>342237</t>
+          <t>341277</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>20055</t>
+          <t>19095</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6549,17 +6549,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ITZEL</t>
+          <t>BRITANY</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>JAVIER</t>
+          <t>BARRIOS</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>HERMITAÑO</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6569,14 +6569,10 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6647715631</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>LAS BRISAS</t>
-        </is>
-      </c>
+          <t>6643289375</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6584,60 +6580,56 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>11-09-2006</t>
+          <t>04-02-2010</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>REYESITZEL152006@GMAIL.COM</t>
+          <t>KUMI142AZUL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>09-02-2026 16:04:59</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
+          <t>05-02-2026 11:41:21</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>11-02-2026 16:19:22</t>
+          <t>05-02-2026 11:42:35</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>11-02-2026 16:18:01</t>
-        </is>
-      </c>
+          <t>05-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6645,23 +6637,19 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26110522268220003063</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26110522103560002549</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>Viridiana Ramirez</t>
+          <t xml:space="preserve"> Daniel  Salinas</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -6935,12 +6923,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>340756</t>
+          <t>342215</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>18574</t>
+          <t>20033</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6950,17 +6938,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LIZETT SINAI</t>
+          <t xml:space="preserve">AMERICA </t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>LUQUIN</t>
+          <t xml:space="preserve">HERRERA </t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t xml:space="preserve">MEZA </t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6970,12 +6958,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6631559835</t>
+          <t>6631239192</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>SAINZ</t>
+          <t xml:space="preserve">VALLE DE LAS PALMAS </t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6985,52 +6973,48 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>16-06-2002</t>
+          <t>11-03-2006</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>LIZETTSINAI00@GMAIL.COM</t>
+          <t>AMERICAHERRERAMEZA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>03-02-2026 17:55:54</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 15:32:32</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>03-02-2026 17:58:43</t>
+          <t>09-02-2026 15:36:39</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>03-02-2026 17:58:14</t>
+          <t>09-02-2026 15:36:02</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -7050,19 +7034,19 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26110522051390002385</t>
+          <t>26110522195800002832</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>Viridiana Ramirez</t>
+          <t xml:space="preserve"> Daniel  Salinas</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -7074,12 +7058,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>341118</t>
+          <t>342237</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>18936</t>
+          <t>20055</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7089,17 +7073,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAVID </t>
+          <t>ITZEL</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOTELO </t>
+          <t>JAVIER</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEDINA </t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7109,32 +7093,32 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6643656598</t>
+          <t>6647715631</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>LA MESA</t>
+          <t>LAS BRISAS</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>18-12-1983</t>
+          <t>11-09-2006</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>SEDIVIDIOLACENA@HOTMAIL.COM</t>
+          <t>REYESITZEL152006@GMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>04-02-2026 17:45:14</t>
+          <t>09-02-2026 16:04:59</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -7145,7 +7129,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -7155,17 +7139,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>04-02-2026 17:47:07</t>
+          <t>11-02-2026 16:19:22</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>04-02-2026 17:46:36</t>
+          <t>11-02-2026 16:18:01</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -7185,10 +7169,14 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26110522083440002492</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr"/>
+          <t>26110522268220003063</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr">
         <is>
@@ -7197,7 +7185,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>Alan Rene Flores Wong</t>
+          <t>Viridiana Ramirez</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -7209,12 +7197,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>341277</t>
+          <t>340756</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>19095</t>
+          <t>18574</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7224,17 +7212,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>BRITANY</t>
+          <t>LIZETT SINAI</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>BARRIOS</t>
+          <t>LUQUIN</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>HERMITAÑO</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7244,10 +7232,14 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6643289375</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>6631559835</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>SAINZ</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7255,17 +7247,17 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>04-02-2010</t>
+          <t>16-06-2002</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>KUMI142AZUL@GMAIL.COM</t>
+          <t>LIZETTSINAI00@GMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>05-02-2026 11:41:21</t>
+          <t>03-02-2026 17:55:54</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7275,36 +7267,44 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>05-02-2026 11:42:35</t>
+          <t>03-02-2026 17:58:43</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr"/>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>03-02-2026 17:58:14</t>
+        </is>
+      </c>
       <c r="U51" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7312,19 +7312,19 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26110522103560002549</t>
+          <t>26110522051390002385</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Daniel  Salinas</t>
+          <t>Viridiana Ramirez</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -7856,12 +7856,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>341753</t>
+          <t>346113</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>19571</t>
+          <t>88278</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7871,17 +7871,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA JAZMIN </t>
+          <t>ANA CRISTINA</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORRRAL </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">VEGA </t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6631060504</t>
+          <t>6641287774</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">GRANJAS FAMILIARES DE MATAMOROS </t>
+          <t>SA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7906,48 +7906,52 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>24-02-1986</t>
+          <t>03-09-1993</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>JAZYAZCORRANV@GMAIL.COM</t>
+          <t>ANA0317LT@GMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>07-02-2026 08:38:48</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
+          <t>24-02-2026 10:28:13</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>07-02-2026 08:44:20</t>
+          <t>24-02-2026 10:32:33</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
+          <t>24-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>07-02-2026 08:43:29</t>
+          <t>24-02-2026 10:32:01</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -7957,7 +7961,7 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
@@ -7967,19 +7971,19 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26110522156430002737</t>
+          <t>26110522615630003885</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Daniel  Salinas</t>
+          <t>Viridiana Ramirez</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -7991,12 +7995,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>346113</t>
+          <t>341753</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>88278</t>
+          <t>19571</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8006,17 +8010,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ANA CRISTINA</t>
+          <t xml:space="preserve">ANA JAZMIN </t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t xml:space="preserve">CORRRAL </t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t xml:space="preserve">VEGA </t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8026,12 +8030,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>6641287774</t>
+          <t>6631060504</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t xml:space="preserve">GRANJAS FAMILIARES DE MATAMOROS </t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -8041,52 +8045,48 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>03-09-1993</t>
+          <t>24-02-1986</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>ANA0317LT@GMAIL.COM</t>
+          <t>JAZYAZCORRANV@GMAIL.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>24-02-2026 10:28:13</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>07-02-2026 08:38:48</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>24-02-2026 10:32:33</t>
+          <t>07-02-2026 08:44:20</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
+          <t>07-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>24-02-2026 10:32:01</t>
+          <t>07-02-2026 08:43:29</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -8106,19 +8106,19 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26110522615630003885</t>
+          <t>26110522156430002737</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>Viridiana Ramirez</t>
+          <t xml:space="preserve"> Daniel  Salinas</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -8269,12 +8269,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>345085</t>
+          <t>342356</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>87250</t>
+          <t>20174</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8284,17 +8284,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">GRACIELA ARACELI </t>
+          <t xml:space="preserve">ERICK </t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t xml:space="preserve">INCLAN </t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLORES </t>
+          <t xml:space="preserve">MENDOZA </t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -8304,79 +8304,63 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>6643645885</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>CUBANOS 16016</t>
-        </is>
-      </c>
+          <t>6642866203</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>19-02-1978</t>
+          <t>19-01-2007</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>BENETTS95@GMAIL.COM</t>
+          <t>ERICKINCLAN71@GMAIL.COM</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>19-02-2026 14:55:25</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>09-02-2026 17:50:49</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIO HTP $599</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>599</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>19-02-2026 14:55:26</t>
+          <t>09-02-2026 17:51:32</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>19-02-2026 14:55:26</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr"/>
       <c r="W59" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8384,14 +8368,14 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>26110522495890003647</t>
+          <t>26110522204250002869</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="inlineStr"/>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>599</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
@@ -8408,12 +8392,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>345131</t>
+          <t>342425</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>87296</t>
+          <t>20243</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8423,17 +8407,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ALFONSO</t>
+          <t xml:space="preserve">EVELYN </t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t xml:space="preserve">VARGAS </t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SANTIBAÑEZ</t>
+          <t xml:space="preserve">MORENO </t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -8443,32 +8427,28 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>6642855092</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>ZONA CENTRO</t>
-        </is>
-      </c>
+          <t>6645745047</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>28-03-1989</t>
+          <t>29-01-2003</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>PEDROALFONSOVALDEZ@GMAIL.COM</t>
+          <t>EVELYNVARGASMORENO02@GMAIL.COM</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>19-02-2026 16:55:34</t>
+          <t>09-02-2026 19:08:21</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -8478,44 +8458,36 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>27-02-2026 20:32:44</t>
+          <t>09-02-2026 19:09:17</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>27-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>27-02-2026 20:31:53</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr"/>
       <c r="W60" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8523,40 +8495,36 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>26110522725960004247</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26110522209750002897</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="inlineStr"/>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alan Rene Flores Wong</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>343587</t>
+          <t>342481</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>21404</t>
+          <t>20298</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8566,17 +8534,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>MONICA VANESSA</t>
+          <t xml:space="preserve">DIEGO ARMANDO </t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ROJO</t>
+          <t>SALAS</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AGUNDIS</t>
+          <t>AVITIA</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -8586,32 +8554,32 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>6644154752</t>
+          <t>6862368233</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>FRACC LAS DELICIAS</t>
+          <t>1 DE MAYO</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>14-09-1998</t>
+          <t>07-03-1989</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>VANEROJO14@GMAIL.COM</t>
+          <t>DS6862368233@GMAIL.COM</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>13-02-2026 18:42:13</t>
+          <t>09-02-2026 20:19:39</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -8622,7 +8590,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -8632,17 +8600,17 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>13-02-2026 18:45:29</t>
+          <t>09-02-2026 20:21:36</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>13-02-2026 18:44:53</t>
+          <t>09-02-2026 20:21:20</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -8662,7 +8630,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>26110522328680003269</t>
+          <t>26110522213470002912</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr"/>
@@ -8674,7 +8642,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>Viridiana Ramirez</t>
+          <t>Alan Rene Flores Wong</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -8686,12 +8654,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>343715</t>
+          <t>345085</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>21532</t>
+          <t>87250</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8701,17 +8669,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>JOHANA</t>
+          <t xml:space="preserve">GRACIELA ARACELI </t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MILLAN</t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SOLIS</t>
+          <t xml:space="preserve">FLORES </t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -8721,12 +8689,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>6646137030</t>
+          <t>6643645885</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>AMPLACION REFORMA</t>
+          <t>CUBANOS 16016</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -8736,20 +8704,24 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>14-01-1993</t>
+          <t>19-02-1978</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>JOHANA_1993@GMAIL.COM</t>
+          <t>BENETTS95@GMAIL.COM</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>14-02-2026 11:52:57</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
+          <t>19-02-2026 14:55:25</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O62" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8767,22 +8739,22 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>15-02-2026 12:23:01</t>
+          <t>19-02-2026 14:55:26</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>15-02-2026 12:20:52</t>
+          <t>19-02-2026 14:55:26</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -8797,14 +8769,10 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>26110522365450003320</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26110522495890003647</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr">
         <is>
@@ -8825,12 +8793,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>342356</t>
+          <t>345131</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>20174</t>
+          <t>87296</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8840,17 +8808,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">ERICK </t>
+          <t>ALFONSO</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">INCLAN </t>
+          <t>VALDEZ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">MENDOZA </t>
+          <t>SANTIBAÑEZ</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -8860,10 +8828,14 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>6642866203</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>6642855092</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>ZONA CENTRO</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -8871,52 +8843,64 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>19-01-2007</t>
+          <t>28-03-1989</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>ERICKINCLAN71@GMAIL.COM</t>
+          <t>PEDROALFONSOVALDEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>09-02-2026 17:50:49</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
+          <t>19-02-2026 16:55:34</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>CONVENIO HTP $599</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>09-02-2026 17:51:32</t>
+          <t>27-02-2026 20:32:44</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T63" t="inlineStr"/>
+          <t>27-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>27-02-2026 20:31:53</t>
+        </is>
+      </c>
       <c r="U63" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V63" t="inlineStr"/>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W63" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8924,36 +8908,40 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>26110522204250002869</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr"/>
+          <t>26110522725960004247</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z63" t="inlineStr"/>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>Viridiana Ramirez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>342425</t>
+          <t>342697</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>20243</t>
+          <t>20514</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -8963,17 +8951,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">EVELYN </t>
+          <t>ESTEFANI</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">VARGAS </t>
+          <t>LÓPEZ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORENO </t>
+          <t>ROBLERO</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -8983,10 +8971,14 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>6645745047</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>6648247825</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>VILLA DEL CAMPO</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -8994,56 +8986,60 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>29-01-2003</t>
+          <t>20-07-2005</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>EVELYNVARGASMORENO02@GMAIL.COM</t>
+          <t>FANI.LUPITA.RL@GMIAL.COM</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>09-02-2026 19:08:21</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 16:12:24</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>09-02-2026 19:09:17</t>
+          <t>13-02-2026 16:52:46</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T64" t="inlineStr"/>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>13-02-2026 16:52:09</t>
+        </is>
+      </c>
       <c r="U64" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V64" t="inlineStr"/>
       <c r="W64" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9051,19 +9047,23 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>26110522209750002897</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr"/>
+          <t>26110522325000003252</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z64" t="inlineStr"/>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>Alan Rene Flores Wong</t>
+          <t>Viridiana Ramirez</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -9075,12 +9075,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>342481</t>
+          <t>346755</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>20298</t>
+          <t>88920</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9090,17 +9090,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIEGO ARMANDO </t>
+          <t xml:space="preserve">KARLA MARIANA </t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>SALAS</t>
+          <t>VARILLA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>AVITIA</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -9110,35 +9110,39 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>6862368233</t>
+          <t>6631133535</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1 DE MAYO</t>
+          <t>NATURA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>07-03-1989</t>
+          <t>20-10-2005</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>DS6862368233@GMAIL.COM</t>
+          <t>KMARYYI.SZL@GHMAIL.COM</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>09-02-2026 20:19:39</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
+          <t>26-02-2026 16:33:59</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O65" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -9146,7 +9150,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -9156,17 +9160,17 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>09-02-2026 20:21:36</t>
+          <t>26-02-2026 16:40:13</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>26-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>09-02-2026 20:21:20</t>
+          <t>26-02-2026 16:39:23</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -9186,7 +9190,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>26110522213470002912</t>
+          <t>26110522687580004118</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr"/>
@@ -9198,7 +9202,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>Alan Rene Flores Wong</t>
+          <t>Viridiana Ramirez</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -9349,12 +9353,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>343121</t>
+          <t>343587</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>20938</t>
+          <t>21404</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9364,17 +9368,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">CESAR </t>
+          <t>MONICA VANESSA</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>LEON</t>
+          <t>ROJO</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>NAJERA</t>
+          <t>AGUNDIS</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -9384,32 +9388,32 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>6648079120</t>
+          <t>6644154752</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>FRACC LAS DELICIAS</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>10-06-2009</t>
+          <t>14-09-1998</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>CESALEO009@ICLOUD.COM</t>
+          <t>VANEROJO14@GMAIL.COM</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>11-02-2026 19:40:53</t>
+          <t>13-02-2026 18:42:13</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -9420,7 +9424,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -9430,17 +9434,17 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>11-02-2026 19:43:18</t>
+          <t>13-02-2026 18:45:29</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>11-02-2026 19:42:45</t>
+          <t>13-02-2026 18:44:53</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -9460,7 +9464,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>26110522277210003106</t>
+          <t>26110522328680003269</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr"/>
@@ -9472,7 +9476,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>Alan Rene Flores Wong</t>
+          <t>Viridiana Ramirez</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
@@ -9484,12 +9488,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>342697</t>
+          <t>343715</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>20514</t>
+          <t>21532</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9499,17 +9503,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ESTEFANI</t>
+          <t>JOHANA</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>LÓPEZ</t>
+          <t>MILLAN</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>ROBLERO</t>
+          <t>SOLIS</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -9519,12 +9523,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>6648247825</t>
+          <t>6646137030</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>VILLA DEL CAMPO</t>
+          <t>AMPLACION REFORMA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -9534,17 +9538,17 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>20-07-2005</t>
+          <t>14-01-1993</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>FANI.LUPITA.RL@GMIAL.COM</t>
+          <t>JOHANA_1993@GMAIL.COM</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>10-02-2026 16:12:24</t>
+          <t>14-02-2026 11:52:57</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -9565,17 +9569,17 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>13-02-2026 16:52:46</t>
+          <t>15-02-2026 12:23:01</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>13-02-2026 16:52:09</t>
+          <t>15-02-2026 12:20:52</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -9595,7 +9599,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>26110522325000003252</t>
+          <t>26110522365450003320</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
@@ -9623,12 +9627,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>346755</t>
+          <t>343121</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>88920</t>
+          <t>20938</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -9638,17 +9642,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">KARLA MARIANA </t>
+          <t xml:space="preserve">CESAR </t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>VARILLA</t>
+          <t>LEON</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>NAJERA</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -9658,39 +9662,35 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>6631133535</t>
+          <t>6648079120</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>NATURA</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>20-10-2005</t>
+          <t>10-06-2009</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>KMARYYI.SZL@GHMAIL.COM</t>
+          <t>CESALEO009@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>26-02-2026 16:33:59</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>11-02-2026 19:40:53</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -9698,7 +9698,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
@@ -9708,17 +9708,17 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>26-02-2026 16:40:13</t>
+          <t>11-02-2026 19:43:18</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>26-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>26-02-2026 16:39:23</t>
+          <t>11-02-2026 19:42:45</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -9738,7 +9738,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>26110522687580004118</t>
+          <t>26110522277210003106</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr"/>
@@ -9750,7 +9750,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>Viridiana Ramirez</t>
+          <t>Alan Rene Flores Wong</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -9889,12 +9889,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>344117</t>
+          <t>343119</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>21934</t>
+          <t>20936</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -9904,17 +9904,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ERIK ABENAMA</t>
+          <t xml:space="preserve">ABRAHAM </t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ROBLERO</t>
+          <t>LEON</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>SANTIZO</t>
+          <t xml:space="preserve">CEJA </t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -9924,10 +9924,14 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>6633769375</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>6188386528</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>SABTA FE LA MESA</t>
+        </is>
+      </c>
       <c r="J71" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -9935,56 +9939,60 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>28-08-2007</t>
+          <t>27-04-1980</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>REDLOWPP85@GMAIL.COM</t>
+          <t>CEJAAABRHAM123@GMAIL.COM</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>16-02-2026 15:14:13</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>11-02-2026 19:34:05</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>16-02-2026 15:15:44</t>
+          <t>11-02-2026 19:37:11</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T71" t="inlineStr"/>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>11-02-2026 19:36:33</t>
+        </is>
+      </c>
       <c r="U71" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V71" t="inlineStr"/>
       <c r="W71" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9992,19 +10000,19 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>26110522392270003388</t>
+          <t>26110522277030003105</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="inlineStr"/>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>Viridiana Ramirez</t>
+          <t>Alan Rene Flores Wong</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -10016,12 +10024,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>343119</t>
+          <t>343863</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>20936</t>
+          <t>21680</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -10031,17 +10039,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">ABRAHAM </t>
+          <t>BLANCA ESTELA</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>LEON</t>
+          <t>ANALCO</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">CEJA </t>
+          <t>BAUTISTA</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -10051,32 +10059,32 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>6188386528</t>
+          <t>6642922150</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>SABTA FE LA MESA</t>
+          <t>LA MESA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>27-04-1980</t>
+          <t>11-12-1960</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>CEJAAABRHAM123@GMAIL.COM</t>
+          <t>BLANCAANALCO98@GMAIL.COM</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>11-02-2026 19:34:05</t>
+          <t>15-02-2026 14:04:11</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -10087,7 +10095,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
@@ -10097,17 +10105,17 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>11-02-2026 19:37:11</t>
+          <t>15-02-2026 15:27:01</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>11-02-2026 19:36:33</t>
+          <t>15-02-2026 14:25:03</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -10117,7 +10125,7 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
@@ -10127,7 +10135,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>26110522277030003105</t>
+          <t>26110522367570003332</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr"/>
@@ -10139,7 +10147,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>Alan Rene Flores Wong</t>
+          <t>Yadira Polo</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
@@ -10151,12 +10159,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>343553</t>
+          <t>343878</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>21370</t>
+          <t>21695</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -10166,17 +10174,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">ASHLEY ARLETH </t>
+          <t>YOZMAR ANTONIO</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">MENDOZA </t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -10186,63 +10194,67 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>6634520921</t>
+          <t>6646135352</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>CAMINO VERDE</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>05-06-2007</t>
+          <t>21-12-1999</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>MNASH8769@GMAIL.COM</t>
+          <t>YOZMAR.ANTONIO@GMAIL.COOM</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>13-02-2026 17:11:05</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
+          <t>15-02-2026 15:35:46</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>13-02-2026 17:15:04</t>
+          <t>15-02-2026 15:40:49</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>13-02-2026 17:14:03</t>
+          <t>15-02-2026 15:39:56</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -10262,14 +10274,14 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>26110522325980003257</t>
+          <t>26110522367610003333</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="inlineStr"/>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
@@ -10286,12 +10298,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>343417</t>
+          <t>343553</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>21234</t>
+          <t>21370</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -10301,17 +10313,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARCOS ADRIÁN </t>
+          <t xml:space="preserve">ASHLEY ARLETH </t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">ABASCAL </t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRUZ </t>
+          <t xml:space="preserve">MENDOZA </t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -10321,32 +10333,32 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>6644985551</t>
+          <t>6634520921</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>VALLES</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>23-03-1987</t>
+          <t>05-06-2007</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>ADRIANABASCAL11@GMAIL.COM</t>
+          <t>MNASH8769@GMAIL.COM</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>13-02-2026 06:37:02</t>
+          <t>13-02-2026 17:11:05</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -10357,7 +10369,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -10367,17 +10379,17 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>15-02-2026 13:17:34</t>
+          <t>13-02-2026 17:15:04</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>15-02-2026 13:16:37</t>
+          <t>13-02-2026 17:14:03</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -10397,7 +10409,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>26110522366390003328</t>
+          <t>26110522325980003257</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr"/>
@@ -10409,7 +10421,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>Yadira Polo</t>
+          <t>Viridiana Ramirez</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
@@ -10421,12 +10433,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>344263</t>
+          <t>344117</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>22080</t>
+          <t>21934</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -10436,17 +10448,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>DULCE YAMILETH</t>
+          <t>ERIK ABENAMA</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>APOLINAR</t>
+          <t>ROBLERO</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>SANTIZO</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -10456,79 +10468,67 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>6634326653</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>SANCHEZ TABOADA</t>
-        </is>
-      </c>
+          <t>6633769375</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>21-10-2006</t>
+          <t>28-08-2007</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>YAMILETH.MENDOZA2110@GMAIL.COM</t>
+          <t>REDLOWPP85@GMAIL.COM</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>16-02-2026 18:10:35</t>
+          <t>16-02-2026 15:14:13</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>17-02-2026 18:23:47</t>
+          <t>16-02-2026 15:15:44</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>17-02-2026 18:13:37</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V75" t="inlineStr"/>
       <c r="W75" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10536,23 +10536,19 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>26110522441290003495</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26110522392270003388</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="inlineStr"/>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>Alan Rene Flores Wong</t>
+          <t>Viridiana Ramirez</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
@@ -10564,12 +10560,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>343863</t>
+          <t>343417</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>21680</t>
+          <t>21234</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -10579,17 +10575,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>BLANCA ESTELA</t>
+          <t xml:space="preserve">MARCOS ADRIÁN </t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ANALCO</t>
+          <t xml:space="preserve">ABASCAL </t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>BAUTISTA</t>
+          <t xml:space="preserve">CRUZ </t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -10599,32 +10595,32 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>6642922150</t>
+          <t>6644985551</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>LA MESA</t>
+          <t>VALLES</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>11-12-1960</t>
+          <t>23-03-1987</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>BLANCAANALCO98@GMAIL.COM</t>
+          <t>ADRIANABASCAL11@GMAIL.COM</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>15-02-2026 14:04:11</t>
+          <t>13-02-2026 06:37:02</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -10645,7 +10641,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>15-02-2026 15:27:01</t>
+          <t>15-02-2026 13:17:34</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -10655,7 +10651,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>15-02-2026 14:25:03</t>
+          <t>15-02-2026 13:16:37</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -10665,7 +10661,7 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W76" t="inlineStr">
@@ -10675,7 +10671,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>26110522367570003332</t>
+          <t>26110522366390003328</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr"/>
@@ -10699,12 +10695,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>343878</t>
+          <t>343833</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>21695</t>
+          <t>21650</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -10714,17 +10710,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>YOZMAR ANTONIO</t>
+          <t>MARIA DE JESUS</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t xml:space="preserve">ESTRADA </t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>DURAN</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -10734,57 +10730,53 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>6646135352</t>
+          <t>6645079142</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>CAMINO VERDE</t>
+          <t>VILLA DEL ALAMO</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>21-12-1999</t>
+          <t>28-10-1986</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>YOZMAR.ANTONIO@GMAIL.COOM</t>
+          <t>MARIADEJESUSESTRADADURAN25901@GMAIL.COM</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>15-02-2026 15:35:46</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>15-02-2026 12:26:38</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>15-02-2026 15:40:49</t>
+          <t>15-02-2026 12:30:44</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -10794,7 +10786,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>15-02-2026 15:39:56</t>
+          <t>15-02-2026 12:29:49</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -10814,19 +10806,19 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>26110522367610003333</t>
+          <t>26110522365580003321</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="inlineStr"/>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>Viridiana Ramirez</t>
+          <t>Yadira Polo</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
@@ -10838,12 +10830,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>343833</t>
+          <t>346985</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>21650</t>
+          <t>89150</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -10853,17 +10845,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>MARIA DE JESUS</t>
+          <t>JESUS ALEXIS</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESTRADA </t>
+          <t xml:space="preserve">DEL CARMEN </t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>DURAN</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -10873,35 +10865,39 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>6645079142</t>
+          <t>6634904309</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>VILLA DEL ALAMO</t>
+          <t xml:space="preserve">C EL ENCANTO </t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>28-10-1986</t>
+          <t>11-07-1996</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>MARIADEJESUSESTRADADURAN25901@GMAIL.COM</t>
+          <t>DELCARMENALEXIS09@GMAIL.COM</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>15-02-2026 12:26:38</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
+          <t>27-02-2026 15:43:06</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O78" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -10919,17 +10915,17 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>15-02-2026 12:30:44</t>
+          <t>27-02-2026 15:47:23</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>27-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>15-02-2026 12:29:49</t>
+          <t>27-02-2026 15:45:28</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -10939,7 +10935,7 @@
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W78" t="inlineStr">
@@ -10949,7 +10945,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>26110522365580003321</t>
+          <t>26110522717070004202</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr"/>
@@ -10961,7 +10957,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>Yadira Polo</t>
+          <t>Viridiana Ramirez</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
@@ -10973,12 +10969,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>344552</t>
+          <t>344335</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>22369</t>
+          <t>22152</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -10988,17 +10984,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">LIZETH GUADALUPE </t>
+          <t>XITLALI</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>MOLINA</t>
+          <t>FONSECA</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -11008,12 +11004,12 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>6647753501</t>
+          <t>6648209711</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>TRES DE OCTUBRE</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -11023,17 +11019,17 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>29-11-2002</t>
+          <t>07-02-1998</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>LGMG1102@GMIAL.COM</t>
+          <t>ANETTEFONSECA79@GMAIL.COM</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>17-02-2026 16:10:55</t>
+          <t>16-02-2026 19:10:54</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -11058,17 +11054,17 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>17-02-2026 16:16:06</t>
+          <t>16-02-2026 19:14:55</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>17-02-2026 16:15:26</t>
+          <t>16-02-2026 19:13:57</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -11088,7 +11084,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>26110522433350003473</t>
+          <t>26110522407680003425</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr"/>
@@ -11100,7 +11096,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>Viridiana Ramirez</t>
+          <t>Alan Rene Flores Wong</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
@@ -11112,12 +11108,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>346985</t>
+          <t>344263</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>89150</t>
+          <t>22080</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -11127,17 +11123,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>JESUS ALEXIS</t>
+          <t>DULCE YAMILETH</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEL CARMEN </t>
+          <t>APOLINAR</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -11147,32 +11143,32 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>6634904309</t>
+          <t>6634326653</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">C EL ENCANTO </t>
+          <t>SANCHEZ TABOADA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>11-07-1996</t>
+          <t>21-10-2006</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>DELCARMENALEXIS09@GMAIL.COM</t>
+          <t>YAMILETH.MENDOZA2110@GMAIL.COM</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>27-02-2026 15:43:06</t>
+          <t>16-02-2026 18:10:35</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -11197,17 +11193,17 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>27-02-2026 15:47:23</t>
+          <t>17-02-2026 18:23:47</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>27-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>27-02-2026 15:45:28</t>
+          <t>17-02-2026 18:13:37</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -11217,7 +11213,7 @@
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W80" t="inlineStr">
@@ -11227,10 +11223,14 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>26110522717070004202</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr"/>
+          <t>26110522441290003495</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z80" t="inlineStr"/>
       <c r="AA80" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>Viridiana Ramirez</t>
+          <t>Alan Rene Flores Wong</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
@@ -11251,12 +11251,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>344335</t>
+          <t>344552</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>22152</t>
+          <t>22369</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>XITLALI</t>
+          <t xml:space="preserve">LIZETH GUADALUPE </t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>FONSECA</t>
+          <t>MOLINA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -11286,12 +11286,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>6648209711</t>
+          <t>6647753501</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>TRES DE OCTUBRE</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>07-02-1998</t>
+          <t>29-11-2002</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>ANETTEFONSECA79@GMAIL.COM</t>
+          <t>LGMG1102@GMIAL.COM</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>16-02-2026 19:10:54</t>
+          <t>17-02-2026 16:10:55</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>16-02-2026 19:14:55</t>
+          <t>17-02-2026 16:16:06</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>16-02-2026 19:13:57</t>
+          <t>17-02-2026 16:15:26</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>26110522407680003425</t>
+          <t>26110522433350003473</t>
         </is>
       </c>
       <c r="Y81" t="inlineStr"/>
@@ -11378,7 +11378,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>Alan Rene Flores Wong</t>
+          <t>Viridiana Ramirez</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
@@ -11390,12 +11390,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>344029</t>
+          <t>344445</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>21846</t>
+          <t>22262</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -11405,17 +11405,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NOE FERNANDO</t>
+          <t xml:space="preserve">GENESIS YOSELIN </t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODELO </t>
+          <t>CARRANZA</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -11425,32 +11425,28 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>6672160389</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
+          <t>6644964596</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>24-07-1991</t>
+          <t>27-12-2006</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>FER_RF_005@HOTMAIL.COM</t>
+          <t>GENESIS_12@GMAIL.COM</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>16-02-2026 12:04:52</t>
+          <t>17-02-2026 11:04:40</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -11460,44 +11456,36 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>16-02-2026 12:07:35</t>
+          <t>23-02-2026 08:59:55</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>16-02-2026 12:07:09</t>
-        </is>
-      </c>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr"/>
       <c r="U82" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V82" t="inlineStr"/>
       <c r="W82" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -11505,14 +11493,18 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>26110522386290003371</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr"/>
+          <t>26110522574390003799</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z82" t="inlineStr"/>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
@@ -11529,12 +11521,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>344228</t>
+          <t>344029</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>22045</t>
+          <t>21846</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -11544,17 +11536,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">DENISSE RUBI </t>
+          <t>NOE FERNANDO</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMOS </t>
+          <t xml:space="preserve">RODELO </t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMPOS </t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -11564,28 +11556,32 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>6677309248</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>6672160389</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>15-01-1991</t>
+          <t>24-07-1991</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>DENIS_RUBY@HOTMAIL.COM</t>
+          <t>FER_RF_005@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>16-02-2026 17:41:22</t>
+          <t>16-02-2026 12:04:52</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -11595,22 +11591,22 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>16-02-2026 17:42:18</t>
+          <t>16-02-2026 12:07:35</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -11618,13 +11614,21 @@
           <t>16-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T83" t="inlineStr"/>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>16-02-2026 12:07:09</t>
+        </is>
+      </c>
       <c r="U83" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V83" t="inlineStr"/>
       <c r="W83" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -11632,19 +11636,19 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>26110522400450003403</t>
+          <t>26110522386290003371</t>
         </is>
       </c>
       <c r="Y83" t="inlineStr"/>
       <c r="Z83" t="inlineStr"/>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>Viridiana Ramirez</t>
+          <t xml:space="preserve"> Daniel  Salinas</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -11656,12 +11660,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>344445</t>
+          <t>344228</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>22262</t>
+          <t>22045</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -11671,17 +11675,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">GENESIS YOSELIN </t>
+          <t xml:space="preserve">DENISSE RUBI </t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>CARRANZA</t>
+          <t xml:space="preserve">RAMOS </t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t xml:space="preserve">CAMPOS </t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -11691,7 +11695,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>6644964596</t>
+          <t>6677309248</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -11702,17 +11706,17 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>27-12-2006</t>
+          <t>15-01-1991</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>GENESIS_12@GMAIL.COM</t>
+          <t>DENIS_RUBY@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>17-02-2026 11:04:40</t>
+          <t>16-02-2026 17:41:22</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -11737,12 +11741,12 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>23-02-2026 08:59:55</t>
+          <t>16-02-2026 17:42:18</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T84" t="inlineStr"/>
@@ -11759,14 +11763,10 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>26110522574390003799</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26110522400450003403</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr"/>
       <c r="Z84" t="inlineStr"/>
       <c r="AA84" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Daniel  Salinas</t>
+          <t>Viridiana Ramirez</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
@@ -11787,12 +11787,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>345622</t>
+          <t>344845</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>87787</t>
+          <t>22662</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -11802,17 +11802,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>MARIA ISABEL</t>
+          <t>EDUARD</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>CORNEJO</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>IBAÑEZ</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -11822,7 +11822,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>6642667917</t>
+          <t>6644066705</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -11832,57 +11832,57 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>22-02-2006</t>
+          <t>16-04-1996</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>CECILIA.FLORES13977@GMAIL.COM</t>
+          <t>CORNEJO6705@GMAIL.COM</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>22-02-2026 13:56:11</t>
+          <t>18-02-2026 15:41:48</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>22-02-2026 13:59:25</t>
+          <t>18-02-2026 15:47:27</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>22-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>22-02-2026 13:58:33</t>
+          <t>18-02-2026 15:46:52</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -11902,24 +11902,24 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>26110522564050003785</t>
+          <t>26110522464750003558</t>
         </is>
       </c>
       <c r="Y85" t="inlineStr"/>
       <c r="Z85" t="inlineStr"/>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Viridiana Ramirez</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -12053,12 +12053,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>344845</t>
+          <t>344106</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>22662</t>
+          <t>21923</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -12068,17 +12068,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>EDUARD</t>
+          <t>AYLIN CAMILA</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>CORNEJO</t>
+          <t>GODINA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>IBAÑEZ</t>
+          <t>VELAZQUEZ</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -12088,79 +12088,67 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>6644066705</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>CAMINO VERDE</t>
-        </is>
-      </c>
+          <t>6648564459</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>16-04-1996</t>
+          <t>16-11-2007</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>CORNEJO6705@GMAIL.COM</t>
+          <t>VELAZQUEZAYLIN2@GMAIL.COM</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>18-02-2026 15:41:48</t>
+          <t>16-02-2026 14:50:40</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>18-02-2026 15:47:27</t>
+          <t>27-02-2026 20:02:41</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>18-02-2026 15:46:52</t>
-        </is>
-      </c>
+          <t>27-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr"/>
       <c r="U87" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V87" t="inlineStr"/>
       <c r="W87" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -12168,36 +12156,40 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>26110522464750003558</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr"/>
+          <t>26110522725420004243</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z87" t="inlineStr"/>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>Viridiana Ramirez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>344106</t>
+          <t>345671</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>21923</t>
+          <t>87836</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -12207,17 +12199,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>AYLIN CAMILA</t>
+          <t>VALERIA PALOMA</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>GODINA</t>
+          <t>GODINEZ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>VELAZQUEZ</t>
+          <t>AVENDAÑO</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -12227,10 +12219,14 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>6648564459</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>6647670982</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
       <c r="J88" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -12238,56 +12234,64 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>16-11-2007</t>
+          <t>23-05-2006</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>VELAZQUEZAYLIN2@GMAIL.COM</t>
+          <t>VALEANDY080@GMAIL.COM</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>16-02-2026 14:50:40</t>
+          <t>23-02-2026 08:12:01</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>27-02-2026 20:02:41</t>
+          <t>25-02-2026 08:25:38</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>27-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T88" t="inlineStr"/>
+          <t>25-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>25-02-2026 08:25:06</t>
+        </is>
+      </c>
       <c r="U88" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V88" t="inlineStr"/>
       <c r="W88" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -12295,28 +12299,28 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>26110522725420004243</t>
+          <t>26110522647040003978</t>
         </is>
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
         </is>
       </c>
       <c r="Z88" t="inlineStr"/>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Marissa  Hernandez Galindo</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -12589,12 +12593,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>345671</t>
+          <t>345622</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>87836</t>
+          <t>87787</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -12604,17 +12608,17 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VALERIA PALOMA</t>
+          <t>MARIA ISABEL</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>GODINEZ</t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>AVENDAÑO</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -12624,12 +12628,12 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>6647670982</t>
+          <t>6642667917</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CAMINO VERDE</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -12639,52 +12643,52 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>23-05-2006</t>
+          <t>22-02-2006</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>VALEANDY080@GMAIL.COM</t>
+          <t>CECILIA.FLORES13977@GMAIL.COM</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>23-02-2026 08:12:01</t>
+          <t>22-02-2026 13:56:11</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>25-02-2026 08:25:38</t>
+          <t>22-02-2026 13:59:25</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
+          <t>22-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>25-02-2026 08:25:06</t>
+          <t>22-02-2026 13:58:33</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -12704,40 +12708,36 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>26110522647040003978</t>
-        </is>
-      </c>
-      <c r="Y91" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26110522564050003785</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr"/>
       <c r="Z91" t="inlineStr"/>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>Marissa  Hernandez Galindo</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>346393</t>
+          <t>345886</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>88558</t>
+          <t>88051</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -12747,99 +12747,87 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>SAHAIRE</t>
+          <t>JONATHAN LEONEL</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>CORTES</t>
+          <t xml:space="preserve">AGUILAR </t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>6633001315</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
+          <t>9096437062</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>20-10-1990</t>
+          <t>12-02-2012</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>SAHAIREC@GMAIL.COM</t>
+          <t>LEO.KARINA16@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>25-02-2026 08:51:13</t>
+          <t>23-02-2026 16:42:13</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>25-02-2026 09:09:48</t>
+          <t>23-02-2026 16:43:25</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T92" t="inlineStr">
-        <is>
-          <t>25-02-2026 09:08:51</t>
-        </is>
-      </c>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr"/>
       <c r="U92" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr"/>
       <c r="W92" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -12847,23 +12835,19 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>26110522648120003988</t>
-        </is>
-      </c>
-      <c r="Y92" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26110522588140003830</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr"/>
       <c r="Z92" t="inlineStr"/>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>Arid Alexis Tolin Caldera</t>
+          <t>Viridiana Ramirez</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
@@ -13562,12 +13546,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>345886</t>
+          <t>346238</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>88051</t>
+          <t>88403</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -13577,27 +13561,27 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>JONATHAN LEONEL</t>
+          <t xml:space="preserve">ISIAS </t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGUILAR </t>
+          <t>LUJAN</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>9096437062</t>
+          <t>6641427798</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -13608,17 +13592,17 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>12-02-2012</t>
+          <t>20-11-2007</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>LEO.KARINA16@ICLOUD.COM</t>
+          <t>IASAISLUJAN6@GMAIL.COM</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>23-02-2026 16:42:13</t>
+          <t>24-02-2026 17:04:16</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -13643,18 +13627,18 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>23-02-2026 16:43:25</t>
+          <t>24-02-2026 17:05:45</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>24-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T98" t="inlineStr"/>
       <c r="U98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V98" t="inlineStr"/>
@@ -13665,7 +13649,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>26110522588140003830</t>
+          <t>26110522626590003930</t>
         </is>
       </c>
       <c r="Y98" t="inlineStr"/>
@@ -13677,7 +13661,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>Viridiana Ramirez</t>
+          <t>Alan Rene Flores Wong</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
@@ -13967,12 +13951,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>346972</t>
+          <t>346393</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>89137</t>
+          <t>88558</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -13982,17 +13966,17 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>GENESIS BRISNEY</t>
+          <t>SAHAIRE</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>SILIS</t>
+          <t>CORTES</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>ZALPA</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -14002,10 +13986,14 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>6631994952</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>6633001315</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
       <c r="J101" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -14013,56 +14001,64 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>23-11-2007</t>
+          <t>20-10-1990</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>BRISNEY.11@GMAIL.COM</t>
+          <t>SAHAIREC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>27-02-2026 15:14:47</t>
+          <t>25-02-2026 08:51:13</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>27-02-2026 15:16:35</t>
+          <t>25-02-2026 09:09:48</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>27-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T101" t="inlineStr"/>
+          <t>25-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>25-02-2026 09:08:51</t>
+        </is>
+      </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V101" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W101" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -14070,36 +14066,40 @@
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>26110522714790004199</t>
-        </is>
-      </c>
-      <c r="Y101" t="inlineStr"/>
+          <t>26110522648120003988</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z101" t="inlineStr"/>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Arid Alexis Tolin Caldera</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>345670</t>
+          <t>346229</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>87835</t>
+          <t>88394</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -14109,17 +14109,17 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>KARO YOSELIN</t>
+          <t>JESVIR MANUEL</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>QUIÑONES</t>
+          <t>CERMEÑO</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>AVILA</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -14129,79 +14129,67 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>6643484664</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
+          <t>6634811026</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>06-02-2007</t>
+          <t>08-06-2006</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>KARITOOQZ@GMAIL.COM</t>
+          <t>MANUELCERMENO08@GMAIL.COM</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>23-02-2026 08:10:58</t>
+          <t>24-02-2026 16:49:57</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>25-02-2026 08:58:08</t>
+          <t>24-02-2026 16:51:11</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T102" t="inlineStr">
-        <is>
-          <t>25-02-2026 08:57:31</t>
-        </is>
-      </c>
+          <t>24-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr"/>
       <c r="U102" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V102" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V102" t="inlineStr"/>
       <c r="W102" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -14209,40 +14197,36 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>26110522647870003985</t>
-        </is>
-      </c>
-      <c r="Y102" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26110522625760003929</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr"/>
       <c r="Z102" t="inlineStr"/>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>Marissa  Hernandez Galindo</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>345132</t>
+          <t>345670</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>87297</t>
+          <t>87835</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -14252,17 +14236,17 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>DIEGO ALEJANDRO</t>
+          <t>KARO YOSELIN</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>LARA</t>
+          <t>QUIÑONES</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>RAMÍREZ</t>
+          <t>AVILA</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -14272,67 +14256,67 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>6641179348</t>
+          <t>6643484664</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>EL PIPILA</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>19-04-1989</t>
+          <t>06-02-2007</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>ALEKSAND.LARA@GMAIL.COM</t>
+          <t>KARITOOQZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>19-02-2026 16:55:49</t>
+          <t>23-02-2026 08:10:58</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>27-02-2026 20:36:37</t>
+          <t>25-02-2026 08:58:08</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>27-03-2026 23:59:59</t>
+          <t>25-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>27-02-2026 20:35:56</t>
+          <t>25-02-2026 08:57:31</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
@@ -14342,7 +14326,7 @@
       </c>
       <c r="V103" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W103" t="inlineStr">
@@ -14352,40 +14336,40 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>26110522726020004249</t>
+          <t>26110522647870003985</t>
         </is>
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
         </is>
       </c>
       <c r="Z103" t="inlineStr"/>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Marissa  Hernandez Galindo</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>345349</t>
+          <t>345132</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>87514</t>
+          <t>87297</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -14395,17 +14379,17 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>OSIRIS AZUCENA</t>
+          <t>DIEGO ALEJANDRO</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>LARA</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>OVILLA</t>
+          <t>RAMÍREZ</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -14415,67 +14399,67 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>6641971605</t>
+          <t>6641179348</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>CAMINO VERDE</t>
+          <t>EL PIPILA</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>04-03-2001</t>
+          <t>19-04-1989</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>OSIRISOVILLA04@GMAIL.COM</t>
+          <t>ALEKSAND.LARA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>20-02-2026 17:04:21</t>
+          <t>19-02-2026 16:55:49</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>20-02-2026 17:09:11</t>
+          <t>27-02-2026 20:36:37</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
+          <t>27-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>20-02-2026 17:07:08</t>
+          <t>27-02-2026 20:35:56</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
@@ -14495,36 +14479,40 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>26110522531360003722</t>
-        </is>
-      </c>
-      <c r="Y104" t="inlineStr"/>
+          <t>26110522726020004249</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z104" t="inlineStr"/>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>Marissa  Hernandez Galindo</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>346229</t>
+          <t>345349</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>88394</t>
+          <t>87514</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -14534,17 +14522,17 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>JESVIR MANUEL</t>
+          <t>OSIRIS AZUCENA</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>CERMEÑO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>OVILLA</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -14554,67 +14542,79 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>6634811026</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>6641971605</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>CAMINO VERDE</t>
+        </is>
+      </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>08-06-2006</t>
+          <t>04-03-2001</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>MANUELCERMENO08@GMAIL.COM</t>
+          <t>OSIRISOVILLA04@GMAIL.COM</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>24-02-2026 16:49:57</t>
+          <t>20-02-2026 17:04:21</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>24-02-2026 16:51:11</t>
+          <t>20-02-2026 17:09:11</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T105" t="inlineStr"/>
+          <t>20-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>20-02-2026 17:07:08</t>
+        </is>
+      </c>
       <c r="U105" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V105" t="inlineStr"/>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W105" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -14622,36 +14622,36 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>26110522625760003929</t>
+          <t>26110522531360003722</t>
         </is>
       </c>
       <c r="Y105" t="inlineStr"/>
       <c r="Z105" t="inlineStr"/>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Marissa  Hernandez Galindo</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>346238</t>
+          <t>346972</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>88403</t>
+          <t>89137</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -14661,17 +14661,17 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISIAS </t>
+          <t>GENESIS BRISNEY</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>LUJAN</t>
+          <t>SILIS</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>ZALPA</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -14681,33 +14681,33 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>6641427798</t>
+          <t>6631994952</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>20-11-2007</t>
+          <t>23-11-2007</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>IASAISLUJAN6@GMAIL.COM</t>
+          <t>BRISNEY.11@GMAIL.COM</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>24-02-2026 17:04:16</t>
+          <t>27-02-2026 15:14:47</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -14717,28 +14717,28 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>24-02-2026 17:05:45</t>
+          <t>27-02-2026 15:16:35</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
+          <t>27-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T106" t="inlineStr"/>
       <c r="U106" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V106" t="inlineStr"/>
@@ -14749,24 +14749,24 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>26110522626590003930</t>
+          <t>26110522714790004199</t>
         </is>
       </c>
       <c r="Y106" t="inlineStr"/>
       <c r="Z106" t="inlineStr"/>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>Alan Rene Flores Wong</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -15055,12 +15055,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>347059</t>
+          <t>346997</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>89224</t>
+          <t>89162</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -15070,17 +15070,17 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>BEATRIZ GUADALUPE</t>
+          <t xml:space="preserve">ERIKA </t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>ONTIVEROS</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>ESQUIVEL</t>
+          <t>ANZUREZ</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -15090,10 +15090,14 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>6641772562</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>6645424460</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>CAMINO VERDE</t>
+        </is>
+      </c>
       <c r="J109" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -15101,42 +15105,42 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>12-12-2002</t>
+          <t>18-05-1980</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>BEATRIZ.ONTIVEROS12@GMAIL.COM</t>
+          <t>HERNANDEZE18050@GMAIL.COM</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>27-02-2026 19:00:23</t>
+          <t>27-02-2026 16:19:15</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>27-02-2026 19:01:44</t>
+          <t>27-02-2026 16:25:33</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
@@ -15144,13 +15148,21 @@
           <t>27-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T109" t="inlineStr"/>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>27-02-2026 16:24:56</t>
+        </is>
+      </c>
       <c r="U109" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V109" t="inlineStr"/>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W109" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -15158,36 +15170,36 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>26110522723940004233</t>
+          <t>26110522718200004209</t>
         </is>
       </c>
       <c r="Y109" t="inlineStr"/>
       <c r="Z109" t="inlineStr"/>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Viridiana Ramirez</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>346997</t>
+          <t>347059</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>89162</t>
+          <t>89224</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -15197,17 +15209,17 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">ERIKA </t>
+          <t>BEATRIZ GUADALUPE</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>ONTIVEROS</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>ANZUREZ</t>
+          <t>ESQUIVEL</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -15217,14 +15229,10 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>6645424460</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>CAMINO VERDE</t>
-        </is>
-      </c>
+          <t>6641772562</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -15232,42 +15240,42 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>18-05-1980</t>
+          <t>12-12-2002</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>HERNANDEZE18050@GMAIL.COM</t>
+          <t>BEATRIZ.ONTIVEROS12@GMAIL.COM</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>27-02-2026 16:19:15</t>
+          <t>27-02-2026 19:00:23</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>27-02-2026 16:25:33</t>
+          <t>27-02-2026 19:01:44</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
@@ -15275,21 +15283,13 @@
           <t>27-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T110" t="inlineStr">
-        <is>
-          <t>27-02-2026 16:24:56</t>
-        </is>
-      </c>
+      <c r="T110" t="inlineStr"/>
       <c r="U110" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V110" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V110" t="inlineStr"/>
       <c r="W110" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -15297,24 +15297,24 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>26110522718200004209</t>
+          <t>26110522723940004233</t>
         </is>
       </c>
       <c r="Y110" t="inlineStr"/>
       <c r="Z110" t="inlineStr"/>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>Viridiana Ramirez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__CARROUSEL TJ.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__CARROUSEL TJ.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AC18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -705,24 +705,24 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alan Rene Flores Wong</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>347356</t>
+          <t>183900</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>89521</t>
+          <t>81407</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -732,17 +732,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGDIELA RADAIN </t>
+          <t>MARIO ALBERTO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORONADO </t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASTILLO </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -752,37 +752,37 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6645996485</t>
+          <t>6641117754</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>VILLADELSOL</t>
+          <t>INFONAVIT LA MESA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>02-06-1989</t>
+          <t>23-09-1991</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>PSIC.MAGCASTILLO@HOTMAIL.COM</t>
+          <t>MARIO.AT.CONSTRUCCION@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>01-03-2026 14:38:59</t>
+          <t>12-07-2023 15:56:21</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -802,17 +802,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>01-03-2026 14:42:40</t>
+          <t>02-03-2026 18:44:44</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>01-03-2026 14:41:50</t>
+          <t>02-03-2026 18:44:14</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26110522770500004301</t>
+          <t>26090522813660002062</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
@@ -971,12 +971,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Viridiana Ramirez</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -1098,24 +1098,24 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Viridiana Ramirez</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>183900</t>
+          <t>347356</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>81407</t>
+          <t>89521</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1125,17 +1125,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MARIO ALBERTO</t>
+          <t xml:space="preserve">MAGDIELA RADAIN </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t xml:space="preserve">CORONADO </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t xml:space="preserve">CASTILLO </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1145,37 +1145,37 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6641117754</t>
+          <t>6645996485</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>INFONAVIT LA MESA</t>
+          <t>VILLADELSOL</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>23-09-1991</t>
+          <t>02-06-1989</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>MARIO.AT.CONSTRUCCION@GMAIL.COM</t>
+          <t>PSIC.MAGCASTILLO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>12-07-2023 15:56:21</t>
+          <t>01-03-2026 14:38:59</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1195,17 +1195,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 18:44:44</t>
+          <t>01-03-2026 14:42:40</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>02-03-2026 18:44:14</t>
+          <t>01-03-2026 14:41:50</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26090522813660002062</t>
+          <t>26110522770500004301</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -1249,12 +1249,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347885</t>
+          <t>348227</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90050</t>
+          <t>90392</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1264,17 +1264,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEDRO BYRON </t>
+          <t>NANCY DE JESUS</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>DELFIN</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6645511001</t>
+          <t>6646283608</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,22 +1295,22 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>22-07-2010</t>
+          <t>03-01-1996</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>BYRO.CHAVEZ121212@GMAIL.COM</t>
+          <t>DELFINNANCY103@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 19:50:40</t>
+          <t>03-03-2026 18:22:07</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1320,28 +1320,28 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-03-2026 19:51:59</t>
+          <t>03-03-2026 18:23:16</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
@@ -1352,14 +1352,14 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26110522818180004446</t>
+          <t>26110522854800004558</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1376,12 +1376,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347888</t>
+          <t>348291</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>90053</t>
+          <t>90456</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1391,17 +1391,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VALERIA GUADALUPE</t>
+          <t>NICOLAS EMMANUEL</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t xml:space="preserve">LEYVA </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>MAJUL</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6645570983</t>
+          <t>6641516887</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CAMINO VERDE</t>
+          <t>22530</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>10-09-1991</t>
+          <t>26-11-1994</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>VGPE.HERRERA@GMAIL.COM</t>
+          <t>NICOLAS.LEYVA1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 19:55:23</t>
+          <t>03-03-2026 20:54:48</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 19:59:33</t>
+          <t>03-03-2026 20:59:53</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>02-03-2026 19:58:49</t>
+          <t>03-03-2026 20:58:59</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26110522818480004447</t>
+          <t>26110522861760004583</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1515,12 +1515,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347723</t>
+          <t>348292</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89888</t>
+          <t>90457</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1530,17 +1530,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>RICARDO</t>
+          <t>MARIA LOURDES</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PIERLUSI</t>
+          <t xml:space="preserve">BARRIOS </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>RICARDO</t>
+          <t>MACIAS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1550,67 +1550,79 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6633316750</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>6647582881</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>PLA DE IGUALA</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>22-06-2008</t>
+          <t>12-02-1991</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>OIWELUSIRICARDO10@GMAIL.COM</t>
+          <t>ITLOURDESBARRIOS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 17:12:51</t>
+          <t>03-03-2026 21:02:44</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-03-2026 17:13:36</t>
+          <t>03-03-2026 21:04:56</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>03-03-2026 21:04:27</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1618,14 +1630,14 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26110522805400004406</t>
+          <t>26110522861790004585</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1642,12 +1654,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347800</t>
+          <t>348030</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89965</t>
+          <t>90195</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1657,17 +1669,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE ANTONIO </t>
+          <t xml:space="preserve">BLANCA </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONZALEZ </t>
+          <t>PAREDES</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRUZ </t>
+          <t>SOLEDAD</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1677,43 +1689,47 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6643551501</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>6645971674</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>SANCHEZ TABOADA</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>05-07-2004</t>
+          <t>06-01-1977</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>JOSEANTONIOGONZALEZ.OFICIAL@GMAIL.COM</t>
+          <t>BLANCA937SOLEDAD@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-03-2026 18:12:53</t>
+          <t>03-03-2026 12:41:25</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1723,21 +1739,29 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-03-2026 18:14:19</t>
+          <t>03-03-2026 12:44:08</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>03-03-2026 12:43:35</t>
+        </is>
+      </c>
       <c r="U10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1745,7 +1769,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26110522810880004426</t>
+          <t>26110522839170004499</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
@@ -1757,24 +1781,24 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Arid Alexis Tolin Caldera</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347845</t>
+          <t>347723</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90010</t>
+          <t>89888</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1784,17 +1808,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>OYUKI YADMIN</t>
+          <t>RICARDO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAZO </t>
+          <t>PIERLUSI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMIREZ </t>
+          <t>RICARDO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1804,57 +1828,53 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6691490591</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>AGUILA</t>
-        </is>
-      </c>
+          <t>6633316750</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>21-10-1980</t>
+          <t>22-06-2008</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>OYUKI_RAZO@HOTMAIL.COM</t>
+          <t>OIWELUSIRICARDO10@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-03-2026 18:42:25</t>
+          <t>02-03-2026 17:12:51</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>02-03-2026 18:47:25</t>
+          <t>02-03-2026 17:13:36</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1862,21 +1882,13 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>02-03-2026 18:46:37</t>
-        </is>
-      </c>
+      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1884,22 +1896,959 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26110522813880004433</t>
+          <t>26110522805400004406</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Viridiana Ramirez</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>347800</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>89965</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JOSE ANTONIO </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GONZALEZ </t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CRUZ </t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>6643551501</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>05-07-2004</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>JOSEANTONIOGONZALEZ.OFICIAL@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:12:53</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:14:19</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>26110522810880004426</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Viridiana Ramirez</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>347845</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>90010</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>OYUKI YADMIN</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAZO </t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAMIREZ </t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>6691490591</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>AGUILA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>21-10-1980</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>OYUKI_RAZO@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:42:25</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>649</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:47:25</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:46:37</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>26110522813880004433</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>347885</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>90050</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PEDRO BYRON </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>CHAVEZ</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>HERRERA</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>6645511001</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>22-07-2010</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>BYRO.CHAVEZ121212@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:50:40</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:51:59</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>26110522818180004446</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>347888</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>90053</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VALERIA GUADALUPE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>HERRERA</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>AGUILAR</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>6645570983</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>CAMINO VERDE</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>10-09-1991</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>VGPE.HERRERA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:55:23</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:59:33</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:58:49</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>26110522818480004447</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>348058</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>90223</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SONIA </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALANIZ </t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>COVARRUBIAS</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>6643606559</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>EL MIRADOR</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>22-12-1976</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>ALEXARYZBETH@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>03-03-2026 14:14:18</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>03-03-2026 14:17:14</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>03-03-2026 14:16:26</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>26110522841190004510</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>348184</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>90349</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LEONARDO FARID </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>MORALES</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>REYNOSO</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>7621112096</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CENTRO </t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>24-05-2010</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>LEOARDORAID@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:38:42</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>CONVENIO DOMICILIADO $549</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:45:43</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:45:07</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>26110522852010004544</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>348111</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>90276</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ITZEL GUADALUPE </t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SOLIS </t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIRADO </t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>6643041009</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>21-04-1992</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>ITZELSSOLI2104@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:13:47</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:15:30</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>26110522846060004530</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__CARROUSEL TJ.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__CARROUSEL TJ.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC18"/>
+  <dimension ref="A1:AC29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>46522</t>
+          <t>183900</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>44382</t>
+          <t>81407</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,19 +593,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA TERESA </t>
+          <t>MARIO ALBERTO</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>LOPEZ</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BAHENA </t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>52</t>
@@ -613,32 +613,32 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6664109414</t>
+          <t>6641117754</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AV ROSARITO</t>
+          <t>INFONAVIT LA MESA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>28-10-1994</t>
+          <t>23-09-1991</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>ANNABAHHENA@GMAIL.COM</t>
+          <t>MARIO.AT.CONSTRUCCION@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>30-08-2021 14:51:14</t>
+          <t>12-07-2023 15:56:21</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02-03-2026 18:26:10</t>
+          <t>02-03-2026 18:44:44</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>02-03-2026 18:25:41</t>
+          <t>02-03-2026 18:44:14</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26110522811920004430</t>
+          <t>26090522813660002062</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
@@ -705,24 +705,24 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Alan Rene Flores Wong</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>183900</t>
+          <t>46522</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>81407</t>
+          <t>44382</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -732,17 +732,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MARIO ALBERTO</t>
+          <t xml:space="preserve">ANA TERESA </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t xml:space="preserve">BAHENA </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -752,32 +752,32 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6641117754</t>
+          <t>6664109414</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>INFONAVIT LA MESA</t>
+          <t>AV ROSARITO</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>23-09-1991</t>
+          <t>28-10-1994</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>MARIO.AT.CONSTRUCCION@GMAIL.COM</t>
+          <t>ANNABAHHENA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>12-07-2023 15:56:21</t>
+          <t>30-08-2021 14:51:14</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 18:44:44</t>
+          <t>02-03-2026 18:26:10</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>02-03-2026 18:44:14</t>
+          <t>02-03-2026 18:25:41</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26090522813660002062</t>
+          <t>26110522811920004430</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
@@ -844,24 +844,24 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alan Rene Flores Wong</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347858</t>
+          <t>345070</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>90023</t>
+          <t>87235</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -871,17 +871,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ANDREA GUADALUPE</t>
+          <t>REGINA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">BERNAL </t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ORTEGA</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6641890019</t>
+          <t>6642347356</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -902,22 +902,22 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>26-08-2007</t>
+          <t>26-11-2008</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>ANDYORTEGA2023@GMAIL.COM</t>
+          <t>REGINA_2008@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-03-2026 18:57:26</t>
+          <t>19-02-2026 13:59:10</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -927,17 +927,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 18:58:49</t>
+          <t>02-03-2026 14:10:53</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -959,14 +959,14 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26110522814810004436</t>
+          <t>26110522794250004359</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -983,12 +983,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>345070</t>
+          <t>347356</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>87235</t>
+          <t>89521</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -998,17 +998,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>REGINA</t>
+          <t xml:space="preserve">MAGDIELA RADAIN </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t xml:space="preserve">CORONADO </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t xml:space="preserve">CASTILLO </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1018,10 +1018,14 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6642347356</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>6645996485</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>VILLADELSOL</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1029,32 +1033,32 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>26-11-2008</t>
+          <t>02-06-1989</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>REGINA_2008@GMAIL.COM</t>
+          <t>PSIC.MAGCASTILLO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>19-02-2026 13:59:10</t>
+          <t>01-03-2026 14:38:59</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1064,21 +1068,29 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 14:10:53</t>
+          <t>01-03-2026 14:42:40</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>01-03-2026 14:41:50</t>
+        </is>
+      </c>
       <c r="U5" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1086,7 +1098,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26110522794250004359</t>
+          <t>26110522770500004301</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
@@ -1098,24 +1110,24 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Viridiana Ramirez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347356</t>
+          <t>346130</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89521</t>
+          <t>88295</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1125,17 +1137,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGDIELA RADAIN </t>
+          <t>PEDRO ADRIAN</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORONADO </t>
+          <t>GARABITO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASTILLO </t>
+          <t>POMPA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1145,47 +1157,39 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6645996485</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>VILLADELSOL</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
+          <t>6641947334</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>02-06-1989</t>
+          <t>23-08-1995</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>PSIC.MAGCASTILLO@HOTMAIL.COM</t>
+          <t>PEDRO_1006@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>01-03-2026 14:38:59</t>
+          <t>24-02-2026 12:11:08</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1195,29 +1199,21 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>01-03-2026 14:42:40</t>
+          <t>04-03-2026 07:56:22</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>01-03-2026 14:41:50</t>
-        </is>
-      </c>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1225,10 +1221,14 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26110522770500004301</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr"/>
+          <t>26110522874810004594</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1249,12 +1249,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>348227</t>
+          <t>347423</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90392</t>
+          <t>89588</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1264,17 +1264,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NANCY DE JESUS</t>
+          <t>CLAUDIA JANETH</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>DELFIN</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>MATA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1284,10 +1284,14 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6646283608</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>6645050218</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>RICARDO FLORES MAGON</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1295,17 +1299,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>03-01-1996</t>
+          <t>05-09-1987</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>DELFINNANCY103@GMAIL.COM</t>
+          <t>CLAUDIA10_@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>03-03-2026 18:22:07</t>
+          <t>02-03-2026 07:28:42</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1315,36 +1319,44 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>03-03-2026 18:23:16</t>
+          <t>04-03-2026 08:13:33</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr"/>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>04-03-2026 08:12:56</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W7" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1352,36 +1364,40 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26110522854800004558</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
+          <t>26110522875400004597</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Marissa  Hernandez Galindo</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>348291</t>
+          <t>348030</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>90456</t>
+          <t>90195</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1391,17 +1407,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NICOLAS EMMANUEL</t>
+          <t xml:space="preserve">BLANCA </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEYVA </t>
+          <t>PAREDES</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MAJUL</t>
+          <t>SOLEDAD</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1411,57 +1427,57 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6641516887</t>
+          <t>6645971674</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>22530</t>
+          <t>SANCHEZ TABOADA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>26-11-1994</t>
+          <t>06-01-1977</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>NICOLAS.LEYVA1@GMAIL.COM</t>
+          <t>BLANCA937SOLEDAD@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>03-03-2026 20:54:48</t>
+          <t>03-03-2026 12:41:25</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>03-03-2026 20:59:53</t>
+          <t>03-03-2026 12:44:08</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1471,7 +1487,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>03-03-2026 20:58:59</t>
+          <t>03-03-2026 12:43:35</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1491,36 +1507,36 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26110522861760004583</t>
+          <t>26110522839170004499</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Arid Alexis Tolin Caldera</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>348292</t>
+          <t>347885</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>90457</t>
+          <t>90050</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1530,17 +1546,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MARIA LOURDES</t>
+          <t xml:space="preserve">PEDRO BYRON </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">BARRIOS </t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MACIAS</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1550,14 +1566,10 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6647582881</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>PLA DE IGUALA</t>
-        </is>
-      </c>
+          <t>6645511001</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1565,64 +1577,56 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>12-02-1991</t>
+          <t>22-07-2010</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>ITLOURDESBARRIOS@GMAIL.COM</t>
+          <t>BYRO.CHAVEZ121212@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>03-03-2026 21:02:44</t>
+          <t>02-03-2026 19:50:40</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>03-03-2026 21:04:56</t>
+          <t>02-03-2026 19:51:59</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>03-03-2026 21:04:27</t>
-        </is>
-      </c>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1630,14 +1634,14 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26110522861790004585</t>
+          <t>26110522818180004446</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1654,12 +1658,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>348030</t>
+          <t>347888</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>90195</t>
+          <t>90053</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1669,17 +1673,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">BLANCA </t>
+          <t>VALERIA GUADALUPE</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PAREDES</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SOLEDAD</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1689,12 +1693,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6645971674</t>
+          <t>6645570983</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SANCHEZ TABOADA</t>
+          <t>CAMINO VERDE</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1704,52 +1708,52 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>06-01-1977</t>
+          <t>10-09-1991</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>BLANCA937SOLEDAD@HOTMAIL.COM</t>
+          <t>VGPE.HERRERA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>03-03-2026 12:41:25</t>
+          <t>02-03-2026 19:55:23</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>03-03-2026 12:44:08</t>
+          <t>02-03-2026 19:59:33</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>03-03-2026 12:43:35</t>
+          <t>02-03-2026 19:58:49</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1759,7 +1763,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1769,36 +1773,36 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26110522839170004499</t>
+          <t>26110522818480004447</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Arid Alexis Tolin Caldera</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347723</t>
+          <t>346140</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>89888</t>
+          <t>88305</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1808,17 +1812,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>RICARDO</t>
+          <t>DAYANA BRISEYDA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PIERLUSI</t>
+          <t>MERAZ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>RICARDO</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1828,33 +1832,29 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6633316750</t>
+          <t>6645186749</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>22-06-2008</t>
+          <t>14-11-2008</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>OIWELUSIRICARDO10@GMAIL.COM</t>
+          <t>DAYANA_10@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-03-2026 17:12:51</t>
+          <t>24-02-2026 12:30:44</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1864,28 +1864,28 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>02-03-2026 17:13:36</t>
+          <t>04-03-2026 07:57:23</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V11" t="inlineStr"/>
@@ -1896,36 +1896,40 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26110522805400004406</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr"/>
+          <t>26110522874870004595</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Viridiana Ramirez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>347800</t>
+          <t>348111</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>89965</t>
+          <t>90276</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1935,17 +1939,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE ANTONIO </t>
+          <t xml:space="preserve">ITZEL GUADALUPE </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONZALEZ </t>
+          <t xml:space="preserve">SOLIS </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRUZ </t>
+          <t xml:space="preserve">TIRADO </t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1955,33 +1959,33 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6643551501</t>
+          <t>6643041009</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>05-07-2004</t>
+          <t>21-04-1992</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>JOSEANTONIOGONZALEZ.OFICIAL@GMAIL.COM</t>
+          <t>ITZELSSOLI2104@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>02-03-2026 18:12:53</t>
+          <t>03-03-2026 16:13:47</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1991,28 +1995,28 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>02-03-2026 18:14:19</t>
+          <t>03-03-2026 16:15:30</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V12" t="inlineStr"/>
@@ -2023,36 +2027,36 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26110522810880004426</t>
+          <t>26110522846060004530</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Viridiana Ramirez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347845</t>
+          <t>347723</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>90010</t>
+          <t>89888</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2062,17 +2066,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>OYUKI YADMIN</t>
+          <t>RICARDO</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAZO </t>
+          <t>PIERLUSI</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMIREZ </t>
+          <t>RICARDO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2082,57 +2086,53 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6691490591</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>AGUILA</t>
-        </is>
-      </c>
+          <t>6633316750</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>21-10-1980</t>
+          <t>22-06-2008</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>OYUKI_RAZO@HOTMAIL.COM</t>
+          <t>OIWELUSIRICARDO10@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>02-03-2026 18:42:25</t>
+          <t>02-03-2026 17:12:51</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>02-03-2026 18:47:25</t>
+          <t>02-03-2026 17:13:36</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -2140,21 +2140,13 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>02-03-2026 18:46:37</t>
-        </is>
-      </c>
+      <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2162,36 +2154,36 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26110522813880004433</t>
+          <t>26110522805400004406</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Viridiana Ramirez</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>347885</t>
+          <t>347800</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>90050</t>
+          <t>89965</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2201,17 +2193,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEDRO BYRON </t>
+          <t xml:space="preserve">JOSE ANTONIO </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t xml:space="preserve">GONZALEZ </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t xml:space="preserve">CRUZ </t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2221,28 +2213,28 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6645511001</t>
+          <t>6643551501</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>22-07-2010</t>
+          <t>05-07-2004</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>BYRO.CHAVEZ121212@GMAIL.COM</t>
+          <t>JOSEANTONIOGONZALEZ.OFICIAL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-03-2026 19:50:40</t>
+          <t>02-03-2026 18:12:53</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2267,7 +2259,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>02-03-2026 19:51:59</t>
+          <t>02-03-2026 18:14:19</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2278,7 +2270,7 @@
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V14" t="inlineStr"/>
@@ -2289,7 +2281,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26110522818180004446</t>
+          <t>26110522810880004426</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
@@ -2301,24 +2293,24 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Viridiana Ramirez</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>347888</t>
+          <t>347845</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90053</t>
+          <t>90010</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2328,17 +2320,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VALERIA GUADALUPE</t>
+          <t>OYUKI YADMIN</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t xml:space="preserve">RAZO </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t xml:space="preserve">RAMIREZ </t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2348,12 +2340,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6645570983</t>
+          <t>6691490591</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>CAMINO VERDE</t>
+          <t>AGUILA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2363,17 +2355,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>10-09-1991</t>
+          <t>21-10-1980</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>VGPE.HERRERA@GMAIL.COM</t>
+          <t>OYUKI_RAZO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>02-03-2026 19:55:23</t>
+          <t>02-03-2026 18:42:25</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2398,7 +2390,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>02-03-2026 19:59:33</t>
+          <t>02-03-2026 18:47:25</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2408,7 +2400,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>02-03-2026 19:58:49</t>
+          <t>02-03-2026 18:46:37</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2428,7 +2420,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26110522818480004447</t>
+          <t>26110522813880004433</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
@@ -2452,12 +2444,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>348058</t>
+          <t>347858</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90223</t>
+          <t>90023</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2467,17 +2459,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">SONIA </t>
+          <t>ANDREA GUADALUPE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALANIZ </t>
+          <t xml:space="preserve">BERNAL </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>COVARRUBIAS</t>
+          <t>ORTEGA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2487,14 +2479,10 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6643606559</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>EL MIRADOR</t>
-        </is>
-      </c>
+          <t>6641890019</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2502,64 +2490,56 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>22-12-1976</t>
+          <t>26-08-2007</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>ALEXARYZBETH@GMAIL.COM</t>
+          <t>ANDYORTEGA2023@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>03-03-2026 14:14:18</t>
+          <t>02-03-2026 18:57:26</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>03-03-2026 14:17:14</t>
+          <t>02-03-2026 18:58:49</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>03-03-2026 14:16:26</t>
-        </is>
-      </c>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2567,36 +2547,36 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26110522841190004510</t>
+          <t>26110522814810004436</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Viridiana Ramirez</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>348184</t>
+          <t>347421</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>90349</t>
+          <t>89586</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2606,17 +2586,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEONARDO FARID </t>
+          <t>VERONICA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>BRIONES</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>REYNOSO</t>
+          <t>GAONA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2626,32 +2606,32 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7621112096</t>
+          <t>6644910863</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">CENTRO </t>
+          <t>SA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>24-05-2010</t>
+          <t>15-09-1994</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>LEOARDORAID@GMAIL.COM</t>
+          <t>VERONICA_10@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>03-03-2026 17:38:42</t>
+          <t>02-03-2026 07:28:40</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2666,27 +2646,27 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>03-03-2026 17:45:43</t>
+          <t>04-03-2026 08:16:45</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>03-03-2026 17:45:07</t>
+          <t>04-03-2026 08:16:22</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2706,36 +2686,40 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26110522852010004544</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr"/>
+          <t>26110522875500004598</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Marissa  Hernandez Galindo</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>348111</t>
+          <t>348195</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>90276</t>
+          <t>90360</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2745,17 +2729,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITZEL GUADALUPE </t>
+          <t>MATIANA CITLALLI</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOLIS </t>
+          <t>ARELLANO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">TIRADO </t>
+          <t>AVILA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2765,10 +2749,14 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6643041009</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>6642847396</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>GERANIOS</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2776,17 +2764,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>21-04-1992</t>
+          <t>04-12-1989</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>ITZELSSOLI2104@GMAIL.COM</t>
+          <t>ARELLANOMATIANA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>03-03-2026 16:13:47</t>
+          <t>03-03-2026 17:48:08</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2796,36 +2784,44 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>03-03-2026 16:15:30</t>
+          <t>04-03-2026 09:09:56</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr"/>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>04-03-2026 09:08:30</t>
+        </is>
+      </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W18" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2833,22 +2829,1495 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26110522846060004530</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr"/>
+          <t>26110522876940004607</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>348227</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>90392</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NANCY DE JESUS</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>DELFIN</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>6646283608</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>03-01-1996</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>DELFINNANCY103@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:22:07</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>899</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:23:16</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>26110522854800004558</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>348058</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>90223</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SONIA </t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALANIZ </t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>COVARRUBIAS</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>6643606559</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>EL MIRADOR</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>22-12-1976</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>ALEXARYZBETH@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>03-03-2026 14:14:18</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>03-03-2026 14:17:14</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>03-03-2026 14:16:26</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>26110522841190004510</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>Arid Alexis Tolin Caldera</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>348184</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>90349</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LEONARDO FARID </t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>MORALES</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>REYNOSO</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>7621112096</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CENTRO </t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>24-05-2010</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>LEOARDORAID@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:38:42</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>CONVENIO DOMICILIADO $549</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:45:43</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:45:07</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>26110522852010004544</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>348423</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>90588</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ELIZABETH</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAMIREZ </t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>GOMEZ</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>6625546726</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>31-01-2007</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>BLUESCOM817@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>04-03-2026 13:37:02</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>04-03-2026 13:38:27</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>26110522881700004631</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>348426</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>90591</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>MICHELLE</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>REYES</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>MONROY</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>6633002646</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>09-11-2007</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>MICHELLE_10@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>04-03-2026 13:43:14</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>04-03-2026 13:53:45</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>26110522882180004633</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>348592</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>90757</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>WILBER ALEXANDER</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>MEDINA</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>DIAZ</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>6643371470</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>CAMINO VERDE</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>23-05-2007</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>WILBERD605@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>04-03-2026 19:21:26</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>04-03-2026 19:34:08</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>04-03-2026 19:26:52</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>26110522897800004692</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>348715</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>90880</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FERNANDO EMANUEL </t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>MORENO</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ASTORGA</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>6641255281</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>08-11-2008</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>FMORENO0823@BC.CONALEP.EDU.MX</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>05-03-2026 15:06:12</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>05-03-2026 15:10:49</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>26110522918420004755</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>348291</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>90456</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NICOLAS EMMANUEL</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LEYVA </t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>MAJUL</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>6641516887</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>22530</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>26-11-1994</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NICOLAS.LEYVA1@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>03-03-2026 20:54:48</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>03-03-2026 20:59:53</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>03-03-2026 20:58:59</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>26110522861760004583</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>348292</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>90457</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>MARIA LOURDES</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BARRIOS </t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>MACIAS</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>6647582881</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>PLA DE IGUALA</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>12-02-1991</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>ITLOURDESBARRIOS@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>03-03-2026 21:02:44</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>03-03-2026 21:04:56</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>03-03-2026 21:04:27</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>26110522861790004585</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>348425</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>90590</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>KARLA VICTORIA</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AARON</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>ELIAS</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>6632179230</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>14-08-2007</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>VICO.AARON14@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>04-03-2026 13:40:12</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>04-03-2026 13:41:05</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>26110522881800004632</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>348635</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>90800</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>MIGUEL ANGEL</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>DOMINGUEZ</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>OCHOA</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>6648465786</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>02-01-1961</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NOMANEJACORREO_@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>05-03-2026 08:50:01</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>05-03-2026 09:01:16</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>05-03-2026 09:00:38</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>26110522911180004720</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__CARROUSEL TJ.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__CARROUSEL TJ.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC29"/>
+  <dimension ref="A1:AC32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>183900</t>
+          <t>346130</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>81407</t>
+          <t>88295</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MARIO ALBERTO</t>
+          <t>PEDRO ADRIAN</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>GARABITO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>POMPA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,47 +613,39 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6641117754</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>INFONAVIT LA MESA</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
+          <t>6641947334</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>23-09-1991</t>
+          <t>23-08-1995</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>MARIO.AT.CONSTRUCCION@GMAIL.COM</t>
+          <t>PEDRO_1006@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>12-07-2023 15:56:21</t>
+          <t>24-02-2026 12:11:08</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -663,29 +655,21 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02-03-2026 18:44:44</t>
+          <t>04-03-2026 07:56:22</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>02-03-2026 18:44:14</t>
-        </is>
-      </c>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -693,10 +677,14 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26090522813660002062</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr"/>
+          <t>26110522874810004594</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
@@ -717,12 +705,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>46522</t>
+          <t>345070</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>44382</t>
+          <t>87235</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -732,17 +720,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA TERESA </t>
+          <t>REGINA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BAHENA </t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -752,14 +740,10 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6664109414</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>AV ROSARITO</t>
-        </is>
-      </c>
+          <t>6642347356</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -767,32 +751,32 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>28-10-1994</t>
+          <t>26-11-2008</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>ANNABAHHENA@GMAIL.COM</t>
+          <t>REGINA_2008@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>30-08-2021 14:51:14</t>
+          <t>19-02-2026 13:59:10</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -802,29 +786,21 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 18:26:10</t>
+          <t>02-03-2026 14:10:53</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>02-03-2026 18:25:41</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -832,7 +808,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26110522811920004430</t>
+          <t>26110522794250004359</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
@@ -844,7 +820,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Alan Rene Flores Wong</t>
+          <t>Viridiana Ramirez</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -856,12 +832,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>345070</t>
+          <t>46522</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>87235</t>
+          <t>44382</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -871,17 +847,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>REGINA</t>
+          <t xml:space="preserve">ANA TERESA </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t xml:space="preserve">BAHENA </t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -891,10 +867,14 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6642347356</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>6664109414</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>AV ROSARITO</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -902,32 +882,32 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>26-11-2008</t>
+          <t>28-10-1994</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>REGINA_2008@GMAIL.COM</t>
+          <t>ANNABAHHENA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>19-02-2026 13:59:10</t>
+          <t>30-08-2021 14:51:14</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -937,21 +917,29 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 14:10:53</t>
+          <t>02-03-2026 18:26:10</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:25:41</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -959,7 +947,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26110522794250004359</t>
+          <t>26110522811920004430</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
@@ -971,7 +959,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Viridiana Ramirez</t>
+          <t>Alan Rene Flores Wong</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -983,12 +971,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347356</t>
+          <t>183900</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89521</t>
+          <t>81407</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -998,17 +986,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGDIELA RADAIN </t>
+          <t>MARIO ALBERTO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORONADO </t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASTILLO </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1018,37 +1006,37 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6645996485</t>
+          <t>6641117754</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>VILLADELSOL</t>
+          <t>INFONAVIT LA MESA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>02-06-1989</t>
+          <t>23-09-1991</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>PSIC.MAGCASTILLO@HOTMAIL.COM</t>
+          <t>MARIO.AT.CONSTRUCCION@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>01-03-2026 14:38:59</t>
+          <t>12-07-2023 15:56:21</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1058,7 +1046,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1068,7 +1056,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>01-03-2026 14:42:40</t>
+          <t>02-03-2026 18:44:44</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1078,7 +1066,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>01-03-2026 14:41:50</t>
+          <t>02-03-2026 18:44:14</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1098,7 +1086,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26110522770500004301</t>
+          <t>26090522813660002062</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
@@ -1110,24 +1098,24 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alan Rene Flores Wong</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>346130</t>
+          <t>346140</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>88295</t>
+          <t>88305</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1137,17 +1125,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PEDRO ADRIAN</t>
+          <t>DAYANA BRISEYDA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GARABITO</t>
+          <t>MERAZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>POMPA</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1157,29 +1145,29 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6641947334</t>
+          <t>6645186749</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>23-08-1995</t>
+          <t>14-11-2008</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>PEDRO_1006@GMAIL.COM</t>
+          <t>DAYANA_10@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>24-02-2026 12:11:08</t>
+          <t>24-02-2026 12:30:44</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1189,22 +1177,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>04-03-2026 07:56:22</t>
+          <t>04-03-2026 07:57:23</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1221,7 +1209,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26110522874810004594</t>
+          <t>26110522874870004595</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1232,7 +1220,7 @@
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1249,12 +1237,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347423</t>
+          <t>347356</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89588</t>
+          <t>89521</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1264,17 +1252,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CLAUDIA JANETH</t>
+          <t xml:space="preserve">MAGDIELA RADAIN </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t xml:space="preserve">CORONADO </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MATA</t>
+          <t xml:space="preserve">CASTILLO </t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1284,12 +1272,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6645050218</t>
+          <t>6645996485</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>RICARDO FLORES MAGON</t>
+          <t>VILLADELSOL</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1299,17 +1287,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>05-09-1987</t>
+          <t>02-06-1989</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLAUDIA10_@GMAIL.COM</t>
+          <t>PSIC.MAGCASTILLO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 07:28:42</t>
+          <t>01-03-2026 14:38:59</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1319,32 +1307,32 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>04-03-2026 08:13:33</t>
+          <t>01-03-2026 14:42:40</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>31-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>04-03-2026 08:12:56</t>
+          <t>01-03-2026 14:41:50</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1364,40 +1352,36 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26110522875400004597</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26110522770500004301</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Marissa  Hernandez Galindo</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>348030</t>
+          <t>347423</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>90195</t>
+          <t>89588</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1407,17 +1391,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">BLANCA </t>
+          <t>CLAUDIA JANETH</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PAREDES</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SOLEDAD</t>
+          <t>MATA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1427,12 +1411,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6645971674</t>
+          <t>6645050218</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SANCHEZ TABOADA</t>
+          <t>RICARDO FLORES MAGON</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1442,42 +1426,42 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>06-01-1977</t>
+          <t>05-09-1987</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>BLANCA937SOLEDAD@HOTMAIL.COM</t>
+          <t>CLAUDIA10_@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>03-03-2026 12:41:25</t>
+          <t>02-03-2026 07:28:42</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>03-03-2026 12:44:08</t>
+          <t>04-03-2026 08:13:33</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1487,7 +1471,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>03-03-2026 12:43:35</t>
+          <t>04-03-2026 08:12:56</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1497,7 +1481,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1507,19 +1491,23 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26110522839170004499</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr"/>
+          <t>26110522875400004597</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Arid Alexis Tolin Caldera</t>
+          <t>Marissa  Hernandez Galindo</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1531,12 +1519,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347885</t>
+          <t>347421</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>90050</t>
+          <t>89586</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1546,17 +1534,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEDRO BYRON </t>
+          <t>VERONICA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>BRIONES</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>GAONA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1566,10 +1554,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6645511001</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>6644910863</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1577,56 +1569,64 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>22-07-2010</t>
+          <t>15-09-1994</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>BYRO.CHAVEZ121212@GMAIL.COM</t>
+          <t>VERONICA_10@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 19:50:40</t>
+          <t>02-03-2026 07:28:40</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-03-2026 19:51:59</t>
+          <t>04-03-2026 08:16:45</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>04-03-2026 08:16:22</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1634,36 +1634,40 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26110522818180004446</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr"/>
+          <t>26110522875500004598</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Marissa  Hernandez Galindo</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347888</t>
+          <t>347858</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>90053</t>
+          <t>90023</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1673,17 +1677,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VALERIA GUADALUPE</t>
+          <t>ANDREA GUADALUPE</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t xml:space="preserve">BERNAL </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>ORTEGA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1693,14 +1697,10 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6645570983</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>CAMINO VERDE</t>
-        </is>
-      </c>
+          <t>6641890019</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1708,17 +1708,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>10-09-1991</t>
+          <t>26-08-2007</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>VGPE.HERRERA@GMAIL.COM</t>
+          <t>ANDYORTEGA2023@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-03-2026 19:55:23</t>
+          <t>02-03-2026 18:57:26</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1728,44 +1728,36 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-03-2026 19:59:33</t>
+          <t>02-03-2026 18:58:49</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>02-03-2026 19:58:49</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1773,36 +1765,36 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26110522818480004447</t>
+          <t>26110522814810004436</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Viridiana Ramirez</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>346140</t>
+          <t>348195</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>88305</t>
+          <t>90360</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1812,17 +1804,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DAYANA BRISEYDA</t>
+          <t>MATIANA CITLALLI</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MERAZ</t>
+          <t>ARELLANO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>AVILA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1832,24 +1824,32 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6645186749</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>6642847396</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>GERANIOS</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>14-11-2008</t>
+          <t>04-12-1989</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>DAYANA_10@GMAIL.COM</t>
+          <t>ARELLANOMATIANA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>24-02-2026 12:30:44</t>
+          <t>03-03-2026 17:48:08</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1859,36 +1859,44 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>04-03-2026 07:57:23</t>
+          <t>04-03-2026 09:09:56</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>04-03-2026 09:08:30</t>
+        </is>
+      </c>
       <c r="U11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1896,7 +1904,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26110522874870004595</t>
+          <t>26110522876940004607</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1907,7 +1915,7 @@
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1924,12 +1932,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>348111</t>
+          <t>348227</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>90276</t>
+          <t>90392</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1939,17 +1947,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITZEL GUADALUPE </t>
+          <t>NANCY DE JESUS</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOLIS </t>
+          <t>DELFIN</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">TIRADO </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1959,7 +1967,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6643041009</t>
+          <t>6646283608</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1970,17 +1978,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>21-04-1992</t>
+          <t>03-01-1996</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>ITZELSSOLI2104@GMAIL.COM</t>
+          <t>DELFINNANCY103@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>03-03-2026 16:13:47</t>
+          <t>03-03-2026 18:22:07</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2005,18 +2013,18 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>03-03-2026 16:15:30</t>
+          <t>03-03-2026 18:23:16</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V12" t="inlineStr"/>
@@ -2027,7 +2035,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26110522846060004530</t>
+          <t>26110522854800004558</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
@@ -2039,24 +2047,24 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alan Rene Flores Wong</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347723</t>
+          <t>347885</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>89888</t>
+          <t>90050</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2066,17 +2074,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>RICARDO</t>
+          <t xml:space="preserve">PEDRO BYRON </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PIERLUSI</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>RICARDO</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2086,28 +2094,28 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6633316750</t>
+          <t>6645511001</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>22-06-2008</t>
+          <t>22-07-2010</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>OIWELUSIRICARDO10@GMAIL.COM</t>
+          <t>BYRO.CHAVEZ121212@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>02-03-2026 17:12:51</t>
+          <t>02-03-2026 19:50:40</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2132,12 +2140,12 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>02-03-2026 17:13:36</t>
+          <t>02-03-2026 19:51:59</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -2154,7 +2162,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26110522805400004406</t>
+          <t>26110522818180004446</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
@@ -2166,7 +2174,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Viridiana Ramirez</t>
+          <t>Alan Rene Flores Wong</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2178,12 +2186,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>347800</t>
+          <t>347888</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>89965</t>
+          <t>90053</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2193,17 +2201,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE ANTONIO </t>
+          <t>VALERIA GUADALUPE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONZALEZ </t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRUZ </t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2213,67 +2221,79 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6643551501</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>6645570983</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>CAMINO VERDE</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>05-07-2004</t>
+          <t>10-09-1991</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>JOSEANTONIOGONZALEZ.OFICIAL@GMAIL.COM</t>
+          <t>VGPE.HERRERA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-03-2026 18:12:53</t>
+          <t>02-03-2026 19:55:23</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>02-03-2026 18:14:19</t>
+          <t>02-03-2026 19:59:33</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:58:49</t>
+        </is>
+      </c>
       <c r="U14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W14" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2281,19 +2301,19 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26110522810880004426</t>
+          <t>26110522818480004447</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Viridiana Ramirez</t>
+          <t>Alan Rene Flores Wong</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2305,12 +2325,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>347845</t>
+          <t>347723</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90010</t>
+          <t>89888</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2320,17 +2340,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>OYUKI YADMIN</t>
+          <t>RICARDO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAZO </t>
+          <t>PIERLUSI</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMIREZ </t>
+          <t>RICARDO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2340,79 +2360,67 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6691490591</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>AGUILA</t>
-        </is>
-      </c>
+          <t>6633316750</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>21-10-1980</t>
+          <t>22-06-2008</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>OYUKI_RAZO@HOTMAIL.COM</t>
+          <t>OIWELUSIRICARDO10@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>02-03-2026 18:42:25</t>
+          <t>02-03-2026 17:12:51</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>02-03-2026 18:47:25</t>
+          <t>02-03-2026 17:13:36</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>02-03-2026 18:46:37</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2420,36 +2428,36 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26110522813880004433</t>
+          <t>26110522805400004406</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Viridiana Ramirez</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>347858</t>
+          <t>347800</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90023</t>
+          <t>89965</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2459,17 +2467,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ANDREA GUADALUPE</t>
+          <t xml:space="preserve">JOSE ANTONIO </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">BERNAL </t>
+          <t xml:space="preserve">GONZALEZ </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ORTEGA</t>
+          <t xml:space="preserve">CRUZ </t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2479,33 +2487,33 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6641890019</t>
+          <t>6643551501</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>26-08-2007</t>
+          <t>05-07-2004</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>ANDYORTEGA2023@GMAIL.COM</t>
+          <t>JOSEANTONIOGONZALEZ.OFICIAL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>02-03-2026 18:57:26</t>
+          <t>02-03-2026 18:12:53</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2515,28 +2523,28 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>02-03-2026 18:58:49</t>
+          <t>02-03-2026 18:14:19</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V16" t="inlineStr"/>
@@ -2547,14 +2555,14 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26110522814810004436</t>
+          <t>26110522810880004426</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2571,12 +2579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>347421</t>
+          <t>347845</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>89586</t>
+          <t>90010</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2586,17 +2594,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VERONICA</t>
+          <t>OYUKI YADMIN</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BRIONES</t>
+          <t xml:space="preserve">RAZO </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>GAONA</t>
+          <t xml:space="preserve">RAMIREZ </t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2606,12 +2614,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6644910863</t>
+          <t>6691490591</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>AGUILA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2621,17 +2629,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>15-09-1994</t>
+          <t>21-10-1980</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>VERONICA_10@GMAIL.COM</t>
+          <t>OYUKI_RAZO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>02-03-2026 07:28:40</t>
+          <t>02-03-2026 18:42:25</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2656,17 +2664,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>04-03-2026 08:16:45</t>
+          <t>02-03-2026 18:47:25</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>04-03-2026 08:16:22</t>
+          <t>02-03-2026 18:46:37</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2686,14 +2694,10 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26110522875500004598</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26110522813880004433</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
@@ -2702,7 +2706,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Marissa  Hernandez Galindo</t>
+          <t>Alan Rene Flores Wong</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2714,12 +2718,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>348195</t>
+          <t>348111</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>90360</t>
+          <t>90276</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2729,17 +2733,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MATIANA CITLALLI</t>
+          <t xml:space="preserve">ITZEL GUADALUPE </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ARELLANO</t>
+          <t xml:space="preserve">SOLIS </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AVILA</t>
+          <t xml:space="preserve">TIRADO </t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2749,14 +2753,10 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6642847396</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>GERANIOS</t>
-        </is>
-      </c>
+          <t>6643041009</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2764,17 +2764,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>04-12-1989</t>
+          <t>21-04-1992</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>ARELLANOMATIANA@GMAIL.COM</t>
+          <t>ITZELSSOLI2104@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>03-03-2026 17:48:08</t>
+          <t>03-03-2026 16:13:47</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2784,44 +2784,36 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>04-03-2026 09:09:56</t>
+          <t>03-03-2026 16:15:30</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>04-03-2026 09:08:30</t>
-        </is>
-      </c>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2829,18 +2821,14 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26110522876940004607</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26110522846060004530</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2857,12 +2845,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>348227</t>
+          <t>348291</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>90392</t>
+          <t>90456</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2872,17 +2860,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NANCY DE JESUS</t>
+          <t>NICOLAS EMMANUEL</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>DELFIN</t>
+          <t xml:space="preserve">LEYVA </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>MAJUL</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2892,28 +2880,32 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6646283608</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>6641516887</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>22530</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>03-01-1996</t>
+          <t>26-11-1994</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>DELFINNANCY103@GMAIL.COM</t>
+          <t>NICOLAS.LEYVA1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>03-03-2026 18:22:07</t>
+          <t>03-03-2026 20:54:48</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2923,36 +2915,44 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>03-03-2026 18:23:16</t>
+          <t>03-03-2026 20:59:53</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>03-03-2026 20:58:59</t>
+        </is>
+      </c>
       <c r="U19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W19" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2960,36 +2960,36 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26110522854800004558</t>
+          <t>26110522861760004583</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alan Rene Flores Wong</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>348058</t>
+          <t>348292</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>90223</t>
+          <t>90457</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2999,17 +2999,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">SONIA </t>
+          <t>MARIA LOURDES</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALANIZ </t>
+          <t xml:space="preserve">BARRIOS </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>COVARRUBIAS</t>
+          <t>MACIAS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6643606559</t>
+          <t>6647582881</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>EL MIRADOR</t>
+          <t>PLA DE IGUALA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3034,52 +3034,52 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>22-12-1976</t>
+          <t>12-02-1991</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>ALEXARYZBETH@GMAIL.COM</t>
+          <t>ITLOURDESBARRIOS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>03-03-2026 14:14:18</t>
+          <t>03-03-2026 21:02:44</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>03-03-2026 14:17:14</t>
+          <t>03-03-2026 21:04:56</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>03-03-2026 14:16:26</t>
+          <t>03-03-2026 21:04:27</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -3099,19 +3099,19 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26110522841190004510</t>
+          <t>26110522861790004585</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Arid Alexis Tolin Caldera</t>
+          <t>Alan Rene Flores Wong</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3123,12 +3123,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>348184</t>
+          <t>348425</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>90349</t>
+          <t>90590</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3138,17 +3138,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEONARDO FARID </t>
+          <t>KARLA VICTORIA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>AARON</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>REYNOSO</t>
+          <t>ELIAS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3158,47 +3158,43 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>7621112096</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CENTRO </t>
-        </is>
-      </c>
+          <t>6632179230</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>24-05-2010</t>
+          <t>14-08-2007</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>LEOARDORAID@GMAIL.COM</t>
+          <t>VICO.AARON14@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>03-03-2026 17:38:42</t>
+          <t>04-03-2026 13:40:12</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -3208,7 +3204,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>03-03-2026 17:45:43</t>
+          <t>04-03-2026 13:41:05</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -3216,21 +3212,13 @@
           <t>03-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>03-03-2026 17:45:07</t>
-        </is>
-      </c>
+      <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3238,7 +3226,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26110522852010004544</t>
+          <t>26110522881800004632</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
@@ -3262,12 +3250,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>348423</t>
+          <t>348426</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>90588</t>
+          <t>90591</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3277,17 +3265,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ELIZABETH</t>
+          <t>MICHELLE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMIREZ </t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>MONROY</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3297,7 +3285,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6625546726</t>
+          <t>6633002646</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3308,17 +3296,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>31-01-2007</t>
+          <t>09-11-2007</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>BLUESCOM817@GMAIL.COM</t>
+          <t>MICHELLE_10@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>04-03-2026 13:37:02</t>
+          <t>04-03-2026 13:43:14</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3343,12 +3331,12 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>04-03-2026 13:38:27</t>
+          <t>04-03-2026 13:53:45</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
@@ -3365,7 +3353,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26110522881700004631</t>
+          <t>26110522882180004633</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
@@ -3389,12 +3377,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>348426</t>
+          <t>348423</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>90591</t>
+          <t>90588</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3404,17 +3392,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MICHELLE</t>
+          <t>ELIZABETH</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t xml:space="preserve">RAMIREZ </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MONROY</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3424,7 +3412,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6633002646</t>
+          <t>6625546726</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3435,17 +3423,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>09-11-2007</t>
+          <t>31-01-2007</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>MICHELLE_10@GMAIL.COM</t>
+          <t>BLUESCOM817@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>04-03-2026 13:43:14</t>
+          <t>04-03-2026 13:37:02</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3470,12 +3458,12 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>04-03-2026 13:53:45</t>
+          <t>04-03-2026 13:38:27</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
@@ -3492,7 +3480,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26110522882180004633</t>
+          <t>26110522881700004631</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
@@ -3516,12 +3504,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>348592</t>
+          <t>348058</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>90757</t>
+          <t>90223</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3531,17 +3519,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>WILBER ALEXANDER</t>
+          <t xml:space="preserve">SONIA </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t xml:space="preserve">ALANIZ </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>COVARRUBIAS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3551,67 +3539,67 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6643371470</t>
+          <t>6643606559</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>CAMINO VERDE</t>
+          <t>EL MIRADOR</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>23-05-2007</t>
+          <t>22-12-1976</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>WILBERD605@GMAIL.COM</t>
+          <t>ALEXARYZBETH@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>04-03-2026 19:21:26</t>
+          <t>03-03-2026 14:14:18</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>04-03-2026 19:34:08</t>
+          <t>03-03-2026 14:17:14</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>04-03-2026 19:26:52</t>
+          <t>03-03-2026 14:16:26</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3631,36 +3619,36 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26110522897800004692</t>
+          <t>26110522841190004510</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Arid Alexis Tolin Caldera</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>348715</t>
+          <t>348184</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>90880</t>
+          <t>90349</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3670,17 +3658,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">FERNANDO EMANUEL </t>
+          <t xml:space="preserve">LEONARDO FARID </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ASTORGA</t>
+          <t>REYNOSO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3690,10 +3678,14 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6641255281</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>7621112096</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CENTRO </t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3701,32 +3693,32 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>08-11-2008</t>
+          <t>24-05-2010</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>FMORENO0823@BC.CONALEP.EDU.MX</t>
+          <t>LEOARDORAID@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>05-03-2026 15:06:12</t>
+          <t>03-03-2026 17:38:42</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -3736,21 +3728,29 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>05-03-2026 15:10:49</t>
+          <t>03-03-2026 17:45:43</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:45:07</t>
+        </is>
+      </c>
       <c r="U25" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr"/>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W25" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3758,7 +3758,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26110522918420004755</t>
+          <t>26110522852010004544</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
@@ -3782,12 +3782,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>348291</t>
+          <t>349158</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>90456</t>
+          <t>91323</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3797,17 +3797,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NICOLAS EMMANUEL</t>
+          <t xml:space="preserve">VICTOR ERNESTO </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEYVA </t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MAJUL</t>
+          <t xml:space="preserve">QUEZADA </t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3817,14 +3817,10 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6641516887</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>22530</t>
-        </is>
-      </c>
+          <t>6644943505</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3832,17 +3828,17 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>26-11-1994</t>
+          <t>27-10-1970</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>NICOLAS.LEYVA1@GMAIL.COM</t>
+          <t>SOYBENDITO70@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>03-03-2026 20:54:48</t>
+          <t>07-03-2026 14:01:40</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3852,44 +3848,36 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>03-03-2026 20:59:53</t>
+          <t>07-03-2026 14:02:39</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>03-03-2026 20:58:59</t>
-        </is>
-      </c>
+          <t>06-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3897,14 +3885,14 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26110522861760004583</t>
+          <t>26110522975930004927</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -3921,12 +3909,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>348292</t>
+          <t>348635</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>90457</t>
+          <t>90800</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3936,17 +3924,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>MARIA LOURDES</t>
+          <t>MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">BARRIOS </t>
+          <t>DOMINGUEZ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MACIAS</t>
+          <t>OCHOA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3956,67 +3944,67 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6647582881</t>
+          <t>6648465786</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>PLA DE IGUALA</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>12-02-1991</t>
+          <t>02-01-1961</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>ITLOURDESBARRIOS@GMAIL.COM</t>
+          <t>NOMANEJACORREO_@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>03-03-2026 21:02:44</t>
+          <t>05-03-2026 08:50:01</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>03-03-2026 21:04:56</t>
+          <t>05-03-2026 09:01:16</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>03-03-2026 21:04:27</t>
+          <t>05-03-2026 09:00:38</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4026,7 +4014,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -4036,14 +4024,14 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26110522861790004585</t>
+          <t>26110522911180004720</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -4060,12 +4048,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>348425</t>
+          <t>349234</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>90590</t>
+          <t>91399</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4075,17 +4063,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>KARLA VICTORIA</t>
+          <t xml:space="preserve">YAMILA </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AARON</t>
+          <t>FLORENCIA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ELIAS</t>
+          <t>DOMINGUEZ</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4095,10 +4083,14 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6632179230</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>6645635356</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>REFUGIO</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4106,32 +4098,32 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>14-08-2007</t>
+          <t>02-11-1996</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>VICO.AARON14@GMAIL.COM</t>
+          <t>YAMDOM96@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>04-03-2026 13:40:12</t>
+          <t>08-03-2026 12:40:46</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -4141,21 +4133,29 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>04-03-2026 13:41:05</t>
+          <t>08-03-2026 12:53:30</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr"/>
+          <t>07-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>08-03-2026 12:52:17</t>
+        </is>
+      </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W28" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4163,7 +4163,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26110522881800004632</t>
+          <t>26110522986390004946</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
@@ -4187,12 +4187,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>348635</t>
+          <t>348030</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>90800</t>
+          <t>90195</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4202,17 +4202,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL</t>
+          <t xml:space="preserve">BLANCA </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>DOMINGUEZ</t>
+          <t>PAREDES</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>OCHOA</t>
+          <t>SOLEDAD</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4222,32 +4222,32 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6648465786</t>
+          <t>6645971674</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>SANCHEZ TABOADA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>02-01-1961</t>
+          <t>06-01-1977</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>NOMANEJACORREO_@GMAIL.COM</t>
+          <t>BLANCA937SOLEDAD@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>05-03-2026 08:50:01</t>
+          <t>03-03-2026 12:41:25</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4272,17 +4272,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>05-03-2026 09:01:16</t>
+          <t>03-03-2026 12:44:08</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>05-03-2026 09:00:38</t>
+          <t>03-03-2026 12:43:35</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26110522911180004720</t>
+          <t>26110522839170004499</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
@@ -4314,10 +4314,415 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
+          <t>Arid Alexis Tolin Caldera</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>348592</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>90757</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>WILBER ALEXANDER</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>MEDINA</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>DIAZ</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>6643371470</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>CAMINO VERDE</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>23-05-2007</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>WILBERD605@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>04-03-2026 19:21:26</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>04-03-2026 19:34:08</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>04-03-2026 19:26:52</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>26110522897800004692</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>348715</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>90880</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FERNANDO EMANUEL </t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>MORENO</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ASTORGA</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>6641255281</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>08-11-2008</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>FMORENO0823@BC.CONALEP.EDU.MX</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>05-03-2026 15:06:12</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>05-03-2026 15:10:49</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>26110522918420004755</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>349261</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>91426</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>MERARI MONSERRAT</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>VALENZUELA</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>PEREZ</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>6634316652</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>CAMINO VERDE</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>27-06-2005</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>VALSITA077@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>08-03-2026 14:11:34</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>CONVENIO DOMICILIADO $549</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>08-03-2026 14:16:20</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>07-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>08-03-2026 14:15:52</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>26110522987700004950</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>
